--- a/input/PL/reg_income.xlsx
+++ b/input/PL/reg_income.xlsx
@@ -16,24 +16,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="156" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="186" uniqueCount="69">
   <si>
-    <t>Description:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This file contains regression estimates used by process I3, capital income. The data suggests there is no private pension income </t>
+    <t>Description</t>
   </si>
   <si>
     <t>Authors:</t>
   </si>
   <si>
-    <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
-  </si>
-  <si>
     <t>Last edit:</t>
   </si>
   <si>
-    <t>12 Jan 2016 AB</t>
+    <t/>
   </si>
   <si>
     <t>Process:</t>
@@ -42,31 +36,73 @@
     <t>Process I1a</t>
   </si>
   <si>
-    <t xml:space="preserve">Logit regression estimates of the probability of receiving capital income </t>
+    <t>Process I1b</t>
   </si>
   <si>
-    <t>Process I1b</t>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>Thisfilecontainsregressiones</t>
+  </si>
+  <si>
+    <t>Ashley Burdett, Aleksandra Kolndrekaj</t>
+  </si>
+  <si>
+    <t>12 Jan 2016 AB</t>
+  </si>
+  <si>
+    <t>Description:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logit regression estimates of the probability of receiving capital income </t>
   </si>
   <si>
     <t>OLS regression estimates (ihs) capital income amount -  who receive capital income</t>
   </si>
   <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>Categorical health variable modelled as continuous</t>
-  </si>
-  <si>
     <t>Regions: PL4 = Polnocno-Zachodni, PL5 = Poludniowo-Zachodni, PL6 = Polnocy, PL10 = Central + East. Poludniowy is the omitted category.</t>
   </si>
   <si>
-    <t>Goodness of fit</t>
+    <t>Goodnessoffit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I1a - Receiving capital income </t>
+  </si>
+  <si>
+    <t>Pseudo R-squared</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>I1b - Capital income amount</t>
+  </si>
+  <si>
+    <t>R-squared</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Chi^2</t>
+  </si>
+  <si>
+    <t>Log likelihood</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
   <si>
     <t>REGRESSOR</t>
-  </si>
-  <si>
-    <t>COEFFICIENT</t>
   </si>
   <si>
     <t>Dgn</t>
@@ -171,22 +207,7 @@
     <t>Constant</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t xml:space="preserve">I1a - Receiving capital income </t>
-  </si>
-  <si>
-    <t>Pseudo R-squared</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Chi^2</t>
-  </si>
-  <si>
-    <t>Log likelihood</t>
+    <t>COEFFICIENT</t>
   </si>
   <si>
     <t>Dhe_Excellent_L1</t>
@@ -203,102 +224,15 @@
   <si>
     <t>Ded_Ln_Ypncp_L2</t>
   </si>
-  <si>
-    <t>I1b - Capital income amount</t>
-  </si>
-  <si>
-    <t>R-squared</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="19">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -309,7 +243,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -317,111 +251,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -435,59 +272,99 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>0</v>
+      <c r="B5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="s">
-        <v>11</v>
+      <c r="A12" t="s">
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -500,63 +377,192 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>52</v>
-      </c>
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1">
         <v>0.36923718321630106</v>
       </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
       <c r="E7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7">
+        <v>25</v>
+      </c>
+      <c r="F7" s="1">
         <v>7242.3376469031637</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1">
         <v>120295</v>
       </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
       <c r="E8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8">
+        <v>26</v>
+      </c>
+      <c r="F8" s="1">
         <v>-26246425.48988726</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="1"/>
+    </row>
     <row r="11">
-      <c r="A11" s="9" t="s">
-        <v>62</v>
-      </c>
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1">
         <v>0.57275336323880777</v>
       </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="1"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14">
+        <v>18</v>
+      </c>
+      <c r="B14" s="1">
         <v>5102</v>
       </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="1"/>
     </row>
   </sheetData>
 </worksheet>
@@ -564,3859 +570,3856 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AK35"/>
+  <dimension ref="A1:AJ35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="L1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="M1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="N1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="O1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="P1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="Q1" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="R1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="S1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="T1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="U1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="V1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="W1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="X1" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="Y1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="Z1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="AA1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="AB1" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="AC1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="AD1" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="AE1" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="AF1" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="AG1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="AH1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AI1" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="AJ1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2">
+        <v>29</v>
+      </c>
+      <c r="B2" s="1">
         <v>0.012102023469571906</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>0.0017839684429095653</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>3.6037439610667873e-06</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>-7.5319419509939201e-09</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>-8.6073922017751659e-05</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>-2.9190640771036787e-06</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>0.00016249816300026749</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>0.00021015222787730886</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>-6.2037916535625602e-06</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>-0.00027638478575770772</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>-2.180539449348378e-05</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <v>2.9263576422582792e-05</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="1">
         <v>-0.0018533988107643984</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="1">
         <v>1.7662270687518945e-06</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="1">
         <v>-0.00010878091798493191</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="1">
         <v>-0.00026238988266270874</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="1">
         <v>-9.0261108637345222e-05</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="1">
         <v>0.00013666374996979032</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="1">
         <v>6.4827808928310161e-06</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="1">
         <v>-1.9362708076021975e-05</v>
       </c>
-      <c r="V2">
+      <c r="V2" s="1">
         <v>-0.00034370944801096669</v>
       </c>
-      <c r="W2">
+      <c r="W2" s="1">
         <v>-0.00038123850361427262</v>
       </c>
-      <c r="X2">
+      <c r="X2" s="1">
         <v>0.00010111795208044614</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" s="1">
         <v>-0.0018928150107869581</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" s="1">
         <v>-0.0016495795900745972</v>
       </c>
-      <c r="AA2">
+      <c r="AA2" s="1">
         <v>-0.0016200699795548121</v>
       </c>
-      <c r="AB2">
+      <c r="AB2" s="1">
         <v>0.00024103573777695759</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="1">
         <v>0.00011924923375726782</v>
       </c>
-      <c r="AD2">
+      <c r="AD2" s="1">
         <v>0.00068840872744593655</v>
       </c>
-      <c r="AE2">
+      <c r="AE2" s="1">
         <v>-1.4353810964534732e-05</v>
       </c>
-      <c r="AF2">
+      <c r="AF2" s="1">
         <v>5.4969938243985219e-06</v>
       </c>
-      <c r="AG2">
+      <c r="AG2" s="1">
         <v>4.0964857850996425e-06</v>
       </c>
-      <c r="AH2">
+      <c r="AH2" s="1">
         <v>2.6431532404241927e-05</v>
       </c>
-      <c r="AI2">
+      <c r="AI2" s="1">
         <v>-1.6121058903087462e-06</v>
       </c>
-      <c r="AJ2">
+      <c r="AJ2" s="1">
         <v>0.00092003743403877721</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3">
+        <v>30</v>
+      </c>
+      <c r="B3" s="1">
         <v>-0.012024119796586357</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>3.6037439610667873e-06</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>7.0735538062781267e-05</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>-6.8334094439382856e-07</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>-0.00010238121450018538</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>-0.0001315476226436587</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>-0.00016407373505335614</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>-0.00010997265222091638</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>1.4759148481518461e-06</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>-3.258224467885619e-06</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>-9.8845548177757527e-06</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>-4.5329169120296061e-06</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>2.058725480647667e-05</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>-1.3038019485763307e-06</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>5.7311346521620054e-05</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>0.00010994771497474394</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>2.6836925680571663e-05</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>-8.9927143420649497e-05</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="1">
         <v>-1.0564010437967523e-05</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="1">
         <v>4.8689167075449156e-06</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="1">
         <v>-0.0005397535906132339</v>
       </c>
-      <c r="W3">
+      <c r="W3" s="1">
         <v>-0.0006404350434870362</v>
       </c>
-      <c r="X3">
+      <c r="X3" s="1">
         <v>-0.00062437417118981332</v>
       </c>
-      <c r="Y3">
+      <c r="Y3" s="1">
         <v>0.00024117800619271573</v>
       </c>
-      <c r="Z3">
+      <c r="Z3" s="1">
         <v>-5.081103497035273e-05</v>
       </c>
-      <c r="AA3">
+      <c r="AA3" s="1">
         <v>8.4966693270198233e-05</v>
       </c>
-      <c r="AB3">
+      <c r="AB3" s="1">
         <v>6.8899636296232181e-05</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="1">
         <v>0.00017327627778686224</v>
       </c>
-      <c r="AD3">
+      <c r="AD3" s="1">
         <v>0.00010350706027987834</v>
       </c>
-      <c r="AE3">
+      <c r="AE3" s="1">
         <v>2.5455467700143824e-05</v>
       </c>
-      <c r="AF3">
+      <c r="AF3" s="1">
         <v>-5.0889411249433603e-06</v>
       </c>
-      <c r="AG3">
+      <c r="AG3" s="1">
         <v>1.3543846875278972e-05</v>
       </c>
-      <c r="AH3">
+      <c r="AH3" s="1">
         <v>2.3196172085687456e-05</v>
       </c>
-      <c r="AI3">
+      <c r="AI3" s="1">
         <v>-2.3439814574275982e-06</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ3" s="1">
         <v>-0.00090510970622816782</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4">
+        <v>31</v>
+      </c>
+      <c r="B4" s="1">
         <v>0.00010351143044259261</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>-7.5319419509939201e-09</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>-6.8334094439382856e-07</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>7.0293246708602374e-09</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>2.9040881057664456e-07</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>6.7354416748710579e-07</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>1.1584699601559268e-06</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>8.719576575935738e-07</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>-1.7364834541882502e-08</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>3.5643596148770685e-09</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>8.0996981190381036e-08</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>3.7955941089545223e-08</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>-2.2101325388588792e-07</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>1.2695629810608e-08</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>-7.7023771389335216e-07</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>-1.3228938614973889e-06</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="1">
         <v>-7.2131062553502718e-07</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <v>2.008934254197254e-07</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="1">
         <v>1.1535814464094304e-07</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="1">
         <v>-3.5064294631734573e-08</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="1">
         <v>4.5020594267030065e-06</v>
       </c>
-      <c r="W4">
+      <c r="W4" s="1">
         <v>5.7596146379166823e-06</v>
       </c>
-      <c r="X4">
+      <c r="X4" s="1">
         <v>5.6402864548445454e-06</v>
       </c>
-      <c r="Y4">
+      <c r="Y4" s="1">
         <v>-1.9889607057155336e-06</v>
       </c>
-      <c r="Z4">
+      <c r="Z4" s="1">
         <v>2.5873068649291832e-07</v>
       </c>
-      <c r="AA4">
+      <c r="AA4" s="1">
         <v>-2.056708152937929e-06</v>
       </c>
-      <c r="AB4">
+      <c r="AB4" s="1">
         <v>-3.4340088257294334e-07</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="1">
         <v>-1.5473365537425886e-06</v>
       </c>
-      <c r="AD4">
+      <c r="AD4" s="1">
         <v>-6.6043267596729649e-07</v>
       </c>
-      <c r="AE4">
+      <c r="AE4" s="1">
         <v>-2.6496693074220172e-07</v>
       </c>
-      <c r="AF4">
+      <c r="AF4" s="1">
         <v>-2.0465625732582261e-08</v>
       </c>
-      <c r="AG4">
+      <c r="AG4" s="1">
         <v>-1.7557529951821934e-07</v>
       </c>
-      <c r="AH4">
+      <c r="AH4" s="1">
         <v>-2.8066445402455033e-07</v>
       </c>
-      <c r="AI4">
+      <c r="AI4" s="1">
         <v>1.9860538207604083e-08</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ4" s="1">
         <v>8.7595031674691282e-06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5">
+        <v>32</v>
+      </c>
+      <c r="B5" s="1">
         <v>-0.26505628074349608</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>-8.6073922017751659e-05</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>-0.00010238121450018538</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>2.9040881057664456e-07</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>0.022509649376950366</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>0.0051379291091789136</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>0.0046736577965619868</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>0.0033121803409664596</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>-5.9066434881303691e-05</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>3.5139342621155517e-06</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>-2.9876964528799627e-06</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>7.7646343264902622e-06</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>0.00011127754768279399</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>1.0712983426535917e-06</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>0.017568890842684808</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>0.017679513365496499</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="1">
         <v>0.018943872478959987</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>0.022204879403266667</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="1">
         <v>0.00011424295502333133</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="1">
         <v>-4.179482706608245e-05</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="1">
         <v>0.021069959305103893</v>
       </c>
-      <c r="W5">
+      <c r="W5" s="1">
         <v>0.021668429543554701</v>
       </c>
-      <c r="X5">
+      <c r="X5" s="1">
         <v>0.02199071377853621</v>
       </c>
-      <c r="Y5">
+      <c r="Y5" s="1">
         <v>0.00032035733632116456</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="1">
         <v>-0.0010386763394041828</v>
       </c>
-      <c r="AA5">
+      <c r="AA5" s="1">
         <v>-0.00026096601753147503</v>
       </c>
-      <c r="AB5">
+      <c r="AB5" s="1">
         <v>-1.4058278600929388e-05</v>
       </c>
-      <c r="AC5">
+      <c r="AC5" s="1">
         <v>-0.00049573150907209537</v>
       </c>
-      <c r="AD5">
+      <c r="AD5" s="1">
         <v>-0.00072073311233299825</v>
       </c>
-      <c r="AE5">
+      <c r="AE5" s="1">
         <v>-0.00017891261782107364</v>
       </c>
-      <c r="AF5">
+      <c r="AF5" s="1">
         <v>-0.00021701697311486993</v>
       </c>
-      <c r="AG5">
+      <c r="AG5" s="1">
         <v>7.8154354526771205e-05</v>
       </c>
-      <c r="AH5">
+      <c r="AH5" s="1">
         <v>4.9433677127690492e-05</v>
       </c>
-      <c r="AI5">
+      <c r="AI5" s="1">
         <v>2.8278999714072446e-05</v>
       </c>
-      <c r="AJ5">
+      <c r="AJ5" s="1">
         <v>-0.021139098024173419</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6">
+        <v>33</v>
+      </c>
+      <c r="B6" s="1">
         <v>-0.029642270462506396</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>-2.9190640771036787e-06</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>-0.0001315476226436587</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>6.7354416748710579e-07</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>0.0051379291091789136</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>0.0087022060424057322</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>0.0045218534705836312</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>0.0033107091242974228</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>-1.4783522699041423e-05</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>-8.6695980747745029e-05</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>8.9566632230749486e-05</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>1.8514237728193609e-05</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>5.7348443287661604e-06</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>1.1618261754155315e-06</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>-0.0025586528642843327</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="1">
         <v>0.00055079472599313861</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="1">
         <v>0.0016005818980460483</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="1">
         <v>0.0048727796495035263</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="1">
         <v>5.9901328818335957e-05</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="1">
         <v>-4.9047598135670604e-05</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="1">
         <v>0.0035966297823325369</v>
       </c>
-      <c r="W6">
+      <c r="W6" s="1">
         <v>0.0043258832201138993</v>
       </c>
-      <c r="X6">
+      <c r="X6" s="1">
         <v>0.0046071574782358907</v>
       </c>
-      <c r="Y6">
+      <c r="Y6" s="1">
         <v>0.00027646246758786073</v>
       </c>
-      <c r="Z6">
+      <c r="Z6" s="1">
         <v>-0.0007603851459399417</v>
       </c>
-      <c r="AA6">
+      <c r="AA6" s="1">
         <v>-0.00026942867940675573</v>
       </c>
-      <c r="AB6">
+      <c r="AB6" s="1">
         <v>4.0004103937288862e-05</v>
       </c>
-      <c r="AC6">
+      <c r="AC6" s="1">
         <v>-0.00028275442142084491</v>
       </c>
-      <c r="AD6">
+      <c r="AD6" s="1">
         <v>-0.00041773354159801816</v>
       </c>
-      <c r="AE6">
+      <c r="AE6" s="1">
         <v>-0.00020680279456231597</v>
       </c>
-      <c r="AF6">
+      <c r="AF6" s="1">
         <v>-0.00029414309973394806</v>
       </c>
-      <c r="AG6">
+      <c r="AG6" s="1">
         <v>-0.00020877533717341399</v>
       </c>
-      <c r="AH6">
+      <c r="AH6" s="1">
         <v>-7.454045390739236e-05</v>
       </c>
-      <c r="AI6">
+      <c r="AI6" s="1">
         <v>2.8253198276150871e-05</v>
       </c>
-      <c r="AJ6">
+      <c r="AJ6" s="1">
         <v>-0.0034325115170165924</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7">
+        <v>34</v>
+      </c>
+      <c r="B7" s="1">
         <v>0.049821334666218922</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>0.00016249816300026749</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>-0.00016407373505335614</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>1.1584699601559268e-06</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>0.0046736577965619868</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>0.0045218534705836312</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>0.0055354356336024769</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>0.0032579695407549975</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>-2.8190271866928858e-05</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>2.9814946317170261e-05</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>5.008189059479413e-05</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>1.4949306487677965e-05</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>-0.00016516923338075993</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>1.6596758887255654e-06</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>0.00026010877247331085</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="1">
         <v>-0.00095032267962347509</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="1">
         <v>0.0011109213906710521</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="1">
         <v>0.0043375047181439755</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="1">
         <v>7.3125986406844147e-05</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="1">
         <v>-5.2713071737930722e-05</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="1">
         <v>0.0033084991486582675</v>
       </c>
-      <c r="W7">
+      <c r="W7" s="1">
         <v>0.0037497640668845544</v>
       </c>
-      <c r="X7">
+      <c r="X7" s="1">
         <v>0.0042417885180778808</v>
       </c>
-      <c r="Y7">
+      <c r="Y7" s="1">
         <v>0.0007381263736963257</v>
       </c>
-      <c r="Z7">
+      <c r="Z7" s="1">
         <v>0.00026311029675399496</v>
       </c>
-      <c r="AA7">
+      <c r="AA7" s="1">
         <v>0.00028401935120043678</v>
       </c>
-      <c r="AB7">
+      <c r="AB7" s="1">
         <v>0.00025190342250615131</v>
       </c>
-      <c r="AC7">
+      <c r="AC7" s="1">
         <v>-4.8813587765730328e-05</v>
       </c>
-      <c r="AD7">
+      <c r="AD7" s="1">
         <v>-0.00042193905191306497</v>
       </c>
-      <c r="AE7">
+      <c r="AE7" s="1">
         <v>-0.00023647467835019023</v>
       </c>
-      <c r="AF7">
+      <c r="AF7" s="1">
         <v>-0.0002092715430329441</v>
       </c>
-      <c r="AG7">
+      <c r="AG7" s="1">
         <v>-0.00010126996629608045</v>
       </c>
-      <c r="AH7">
+      <c r="AH7" s="1">
         <v>-3.0030860401207321e-05</v>
       </c>
-      <c r="AI7">
+      <c r="AI7" s="1">
         <v>9.0338800025934526e-06</v>
       </c>
-      <c r="AJ7">
+      <c r="AJ7" s="1">
         <v>-0.0030527299963288078</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8">
+        <v>35</v>
+      </c>
+      <c r="B8" s="1">
         <v>-0.013565508444711794</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>0.00021015222787730886</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>-0.00010997265222091638</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>8.719576575935738e-07</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>0.0033121803409664596</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>0.0033107091242974228</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>0.0032579695407549975</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>0.0038404622479447123</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>-9.3023565088517775e-06</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>-1.7496251772888911e-05</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>1.9996183669980476e-05</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>1.2730484467751799e-05</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>-0.00014529071789158565</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>-6.3177901216857229e-07</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>7.1817749711419743e-05</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="1">
         <v>0.00011162383090374971</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="1">
         <v>-0.00070125748488011343</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="1">
         <v>0.0030730265186940612</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="1">
         <v>4.6637510778960178e-05</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="1">
         <v>-5.9330133662844352e-05</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="1">
         <v>0.0013563238640281455</v>
       </c>
-      <c r="W8">
+      <c r="W8" s="1">
         <v>0.0015397498999126927</v>
       </c>
-      <c r="X8">
+      <c r="X8" s="1">
         <v>0.001846139727709119</v>
       </c>
-      <c r="Y8">
+      <c r="Y8" s="1">
         <v>0.0006309764368931099</v>
       </c>
-      <c r="Z8">
+      <c r="Z8" s="1">
         <v>0.00014071430887927625</v>
       </c>
-      <c r="AA8">
+      <c r="AA8" s="1">
         <v>0.00010749732504297319</v>
       </c>
-      <c r="AB8">
+      <c r="AB8" s="1">
         <v>3.351913522857869e-05</v>
       </c>
-      <c r="AC8">
+      <c r="AC8" s="1">
         <v>-4.8870536680912071e-06</v>
       </c>
-      <c r="AD8">
+      <c r="AD8" s="1">
         <v>-0.00044403147016587222</v>
       </c>
-      <c r="AE8">
+      <c r="AE8" s="1">
         <v>-0.00018431744315230156</v>
       </c>
-      <c r="AF8">
+      <c r="AF8" s="1">
         <v>-0.00019583788490697561</v>
       </c>
-      <c r="AG8">
+      <c r="AG8" s="1">
         <v>-5.136319816392463e-05</v>
       </c>
-      <c r="AH8">
+      <c r="AH8" s="1">
         <v>-8.6017566017499228e-05</v>
       </c>
-      <c r="AI8">
+      <c r="AI8" s="1">
         <v>-3.9977422719899354e-06</v>
       </c>
-      <c r="AJ8">
+      <c r="AJ8" s="1">
         <v>-0.0015780156982079727</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9">
+        <v>36</v>
+      </c>
+      <c r="B9" s="1">
         <v>0.71387067633230339</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>-6.2037916535625602e-06</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>1.4759148481518461e-06</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>-1.7364834541882502e-08</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>-5.9066434881303691e-05</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>-1.4783522699041423e-05</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>-2.8190271866928858e-05</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>-9.3023565088517775e-06</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>0.00018712465047909964</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>-1.9554724075798214e-05</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>3.6357501632652976e-06</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>-9.5936103947530783e-05</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>6.1109082969236462e-05</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>-8.055813554990934e-07</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>-2.3579531706637614e-05</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>-3.8269578004178498e-05</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="1">
         <v>-4.6463884831110785e-05</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="1">
         <v>-0.00014952514504657438</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="1">
         <v>-0.00017319083128352944</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="1">
         <v>0.00013134303715893689</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="1">
         <v>-0.0004038364205639807</v>
       </c>
-      <c r="W9">
+      <c r="W9" s="1">
         <v>-0.00043605887568286695</v>
       </c>
-      <c r="X9">
+      <c r="X9" s="1">
         <v>-0.00046525441437811436</v>
       </c>
-      <c r="Y9">
+      <c r="Y9" s="1">
         <v>-0.00010913946944126323</v>
       </c>
-      <c r="Z9">
+      <c r="Z9" s="1">
         <v>-0.00014877135159677404</v>
       </c>
-      <c r="AA9">
+      <c r="AA9" s="1">
         <v>-0.00013475057093880635</v>
       </c>
-      <c r="AB9">
+      <c r="AB9" s="1">
         <v>-1.4556045232093979e-05</v>
       </c>
-      <c r="AC9">
+      <c r="AC9" s="1">
         <v>-2.239016202774116e-05</v>
       </c>
-      <c r="AD9">
+      <c r="AD9" s="1">
         <v>-4.2531026579442433e-05</v>
       </c>
-      <c r="AE9">
+      <c r="AE9" s="1">
         <v>-4.9144655130532115e-05</v>
       </c>
-      <c r="AF9">
+      <c r="AF9" s="1">
         <v>-3.760810596449843e-05</v>
       </c>
-      <c r="AG9">
+      <c r="AG9" s="1">
         <v>-5.7114362777859906e-05</v>
       </c>
-      <c r="AH9">
+      <c r="AH9" s="1">
         <v>-2.0336837245263661e-05</v>
       </c>
-      <c r="AI9">
+      <c r="AI9" s="1">
         <v>4.3145150942345822e-06</v>
       </c>
-      <c r="AJ9">
+      <c r="AJ9" s="1">
         <v>0.00043247072984436285</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10">
+        <v>37</v>
+      </c>
+      <c r="B10" s="1">
         <v>0.055358506235970363</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>-0.00027638478575770772</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>-3.258224467885619e-06</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>3.5643596148770685e-09</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>3.5139342621155517e-06</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>-8.6695980747745029e-05</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>2.9814946317170261e-05</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>-1.7496251772888911e-05</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>-1.9554724075798214e-05</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0.0021042286603153324</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>-0.00013212240270367963</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>-2.845292745130547e-05</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>0.00025592111601778272</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>-4.5670249671473843e-07</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="1">
         <v>0.0002903713749994475</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="1">
         <v>0.00013432930131396757</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>0.00013455033009500622</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="1">
         <v>0.00010753582804176555</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="1">
         <v>1.7320979083480879e-05</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="1">
         <v>2.4349663944748064e-05</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="1">
         <v>0.000237833754587246</v>
       </c>
-      <c r="W10">
+      <c r="W10" s="1">
         <v>0.00020429692557313444</v>
       </c>
-      <c r="X10">
+      <c r="X10" s="1">
         <v>-0.00050355549718590653</v>
       </c>
-      <c r="Y10">
+      <c r="Y10" s="1">
         <v>0.014062837341612913</v>
       </c>
-      <c r="Z10">
+      <c r="Z10" s="1">
         <v>0.014215474860256046</v>
       </c>
-      <c r="AA10">
+      <c r="AA10" s="1">
         <v>0.014151921554778792</v>
       </c>
-      <c r="AB10">
+      <c r="AB10" s="1">
         <v>-0.00022320505019344351</v>
       </c>
-      <c r="AC10">
+      <c r="AC10" s="1">
         <v>-4.0828430524779261e-05</v>
       </c>
-      <c r="AD10">
+      <c r="AD10" s="1">
         <v>-2.0518222535116388e-05</v>
       </c>
-      <c r="AE10">
+      <c r="AE10" s="1">
         <v>-1.0812774204390502e-07</v>
       </c>
-      <c r="AF10">
+      <c r="AF10" s="1">
         <v>5.2985777610397916e-05</v>
       </c>
-      <c r="AG10">
+      <c r="AG10" s="1">
         <v>1.8751441248913286e-05</v>
       </c>
-      <c r="AH10">
+      <c r="AH10" s="1">
         <v>-3.0605399630216461e-05</v>
       </c>
-      <c r="AI10">
+      <c r="AI10" s="1">
         <v>-2.289211513618666e-05</v>
       </c>
-      <c r="AJ10">
+      <c r="AJ10" s="1">
         <v>-0.013487811945752215</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11">
+        <v>38</v>
+      </c>
+      <c r="B11" s="1">
         <v>0.012228543303695383</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>-2.180539449348378e-05</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>-9.8845548177757527e-06</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>8.0996981190381036e-08</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>-2.9876964528799627e-06</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>8.9566632230749486e-05</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>5.008189059479413e-05</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>1.9996183669980476e-05</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>3.6357501632652976e-06</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>-0.00013212240270367963</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>0.00013613315843239693</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>6.5093351714360291e-06</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>1.554106727053043e-05</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>1.1888531883504101e-07</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="1">
         <v>-5.8810712924420841e-05</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="1">
         <v>-3.1060536800473054e-05</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="1">
         <v>-4.5534078948732888e-06</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="1">
         <v>1.9871520390568826e-05</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="1">
         <v>-5.3462092672487571e-06</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="1">
         <v>-8.7497160120588158e-06</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="1">
         <v>5.3609801850538341e-05</v>
       </c>
-      <c r="W11">
+      <c r="W11" s="1">
         <v>1.3378334471041314e-05</v>
       </c>
-      <c r="X11">
+      <c r="X11" s="1">
         <v>-2.4191708849444521e-05</v>
       </c>
-      <c r="Y11">
+      <c r="Y11" s="1">
         <v>-0.00018906383220897632</v>
       </c>
-      <c r="Z11">
+      <c r="Z11" s="1">
         <v>-0.00019371695188810328</v>
       </c>
-      <c r="AA11">
+      <c r="AA11" s="1">
         <v>-0.0001074363380637266</v>
       </c>
-      <c r="AB11">
+      <c r="AB11" s="1">
         <v>-2.4904729257543503e-05</v>
       </c>
-      <c r="AC11">
+      <c r="AC11" s="1">
         <v>2.4589708721563788e-05</v>
       </c>
-      <c r="AD11">
+      <c r="AD11" s="1">
         <v>5.5029753541514097e-05</v>
       </c>
-      <c r="AE11">
+      <c r="AE11" s="1">
         <v>7.0147238271235212e-06</v>
       </c>
-      <c r="AF11">
+      <c r="AF11" s="1">
         <v>1.7425704554239318e-05</v>
       </c>
-      <c r="AG11">
+      <c r="AG11" s="1">
         <v>1.113046996905053e-06</v>
       </c>
-      <c r="AH11">
+      <c r="AH11" s="1">
         <v>1.0164044238391507e-05</v>
       </c>
-      <c r="AI11">
+      <c r="AI11" s="1">
         <v>1.9581124250593224e-06</v>
       </c>
-      <c r="AJ11">
+      <c r="AJ11" s="1">
         <v>0.00023705757003686758</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12">
+        <v>39</v>
+      </c>
+      <c r="B12" s="1">
         <v>0.37023477931560272</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>2.9263576422582792e-05</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>-4.5329169120296061e-06</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>3.7955941089545223e-08</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>7.7646343264902622e-06</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>1.8514237728193609e-05</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>1.4949306487677965e-05</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>1.2730484467751799e-05</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>-9.5936103947530783e-05</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>-2.845292745130547e-05</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>6.5093351714360291e-06</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>0.0001966295999056486</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="1">
         <v>-5.2834301437977101e-05</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="1">
         <v>5.982433641859535e-07</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="1">
         <v>-4.92187563628744e-05</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="1">
         <v>4.8331764270175233e-06</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="1">
         <v>-5.7343848907391074e-05</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="1">
         <v>4.1875175672900111e-05</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="1">
         <v>8.4159432628448208e-05</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="1">
         <v>-0.00023382115944873489</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="1">
         <v>0.00016874927418075269</v>
       </c>
-      <c r="W12">
+      <c r="W12" s="1">
         <v>0.00015401825424141388</v>
       </c>
-      <c r="X12">
+      <c r="X12" s="1">
         <v>0.00021753172117052014</v>
       </c>
-      <c r="Y12">
+      <c r="Y12" s="1">
         <v>-9.1862754256928625e-05</v>
       </c>
-      <c r="Z12">
+      <c r="Z12" s="1">
         <v>-0.00012078421688511324</v>
       </c>
-      <c r="AA12">
+      <c r="AA12" s="1">
         <v>-9.3792284166807245e-05</v>
       </c>
-      <c r="AB12">
+      <c r="AB12" s="1">
         <v>-1.5419250900175327e-05</v>
       </c>
-      <c r="AC12">
+      <c r="AC12" s="1">
         <v>-5.8223042586120226e-05</v>
       </c>
-      <c r="AD12">
+      <c r="AD12" s="1">
         <v>-5.0383729666441494e-05</v>
       </c>
-      <c r="AE12">
+      <c r="AE12" s="1">
         <v>2.0333099405035096e-05</v>
       </c>
-      <c r="AF12">
+      <c r="AF12" s="1">
         <v>3.2689367787681825e-05</v>
       </c>
-      <c r="AG12">
+      <c r="AG12" s="1">
         <v>-2.6975695680765777e-06</v>
       </c>
-      <c r="AH12">
+      <c r="AH12" s="1">
         <v>2.2541244670759591e-05</v>
       </c>
-      <c r="AI12">
+      <c r="AI12" s="1">
         <v>-1.5489790493394847e-06</v>
       </c>
-      <c r="AJ12">
+      <c r="AJ12" s="1">
         <v>1.3874728153586675e-05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13">
+        <v>40</v>
+      </c>
+      <c r="B13" s="1">
         <v>-0.10373929832110693</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>-0.0018533988107643984</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>2.058725480647667e-05</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>-2.2101325388588792e-07</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>0.00011127754768279399</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>5.7348443287661604e-06</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>-0.00016516923338075993</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>-0.00014529071789158565</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>6.1109082969236462e-05</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>0.00025592111601778272</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>1.554106727053043e-05</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="1">
         <v>-5.2834301437977101e-05</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="1">
         <v>0.032244024285235873</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="1">
         <v>6.4090854597056869e-06</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="1">
         <v>-0.0070759917537936085</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="1">
         <v>0.00012921222998098138</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="1">
         <v>-0.002717106252101989</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="1">
         <v>-0.0032864514040665781</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="1">
         <v>-0.0011954039098147149</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="1">
         <v>-0.00098085062576415785</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="1">
         <v>0.013588647030462395</v>
       </c>
-      <c r="W13">
+      <c r="W13" s="1">
         <v>0.01372108754692636</v>
       </c>
-      <c r="X13">
+      <c r="X13" s="1">
         <v>0.013264811887667771</v>
       </c>
-      <c r="Y13">
+      <c r="Y13" s="1">
         <v>0.0029928128904984663</v>
       </c>
-      <c r="Z13">
+      <c r="Z13" s="1">
         <v>0.001481843575664883</v>
       </c>
-      <c r="AA13">
+      <c r="AA13" s="1">
         <v>0.0014790213580939903</v>
       </c>
-      <c r="AB13">
+      <c r="AB13" s="1">
         <v>-0.00025598036844772865</v>
       </c>
-      <c r="AC13">
+      <c r="AC13" s="1">
         <v>-1.1142196836181045e-05</v>
       </c>
-      <c r="AD13">
+      <c r="AD13" s="1">
         <v>-0.00090919513640622986</v>
       </c>
-      <c r="AE13">
+      <c r="AE13" s="1">
         <v>0.00054603248295070211</v>
       </c>
-      <c r="AF13">
+      <c r="AF13" s="1">
         <v>0.00018010415054083451</v>
       </c>
-      <c r="AG13">
+      <c r="AG13" s="1">
         <v>0.00015228951832689519</v>
       </c>
-      <c r="AH13">
+      <c r="AH13" s="1">
         <v>0.00016018630743554717</v>
       </c>
-      <c r="AI13">
+      <c r="AI13" s="1">
         <v>2.4524342602590338e-05</v>
       </c>
-      <c r="AJ13">
+      <c r="AJ13" s="1">
         <v>-0.01529211463927518</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14">
+        <v>41</v>
+      </c>
+      <c r="B14" s="1">
         <v>-0.0010270612601991672</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>1.7662270687518945e-06</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>-1.3038019485763307e-06</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>1.2695629810608e-08</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>1.0712983426535917e-06</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>1.1618261754155315e-06</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>1.6596758887255654e-06</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>-6.3177901216857229e-07</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>-8.055813554990934e-07</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>-4.5670249671473843e-07</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>1.1888531883504101e-07</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <v>5.982433641859535e-07</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="1">
         <v>6.4090854597056869e-06</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="1">
         <v>1.4074488877298183e-06</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="1">
         <v>-1.2313822634882186e-05</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="1">
         <v>-6.9409438370631528e-05</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="1">
         <v>-4.7350625022449824e-05</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="1">
         <v>-4.6332056702456508e-05</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="1">
         <v>-4.9277919397303619e-06</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="1">
         <v>-2.4536933050857528e-05</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="1">
         <v>0.00050901928451731432</v>
       </c>
-      <c r="W14">
+      <c r="W14" s="1">
         <v>0.00050929086983935367</v>
       </c>
-      <c r="X14">
+      <c r="X14" s="1">
         <v>0.00051089160135695932</v>
       </c>
-      <c r="Y14">
+      <c r="Y14" s="1">
         <v>-1.5100629061880676e-05</v>
       </c>
-      <c r="Z14">
+      <c r="Z14" s="1">
         <v>-1.7922132219900104e-06</v>
       </c>
-      <c r="AA14">
+      <c r="AA14" s="1">
         <v>-3.3485194414020509e-06</v>
       </c>
-      <c r="AB14">
+      <c r="AB14" s="1">
         <v>2.5329416967349277e-06</v>
       </c>
-      <c r="AC14">
+      <c r="AC14" s="1">
         <v>-6.7862380130840943e-06</v>
       </c>
-      <c r="AD14">
+      <c r="AD14" s="1">
         <v>4.842852267768178e-06</v>
       </c>
-      <c r="AE14">
+      <c r="AE14" s="1">
         <v>2.6705214604590957e-06</v>
       </c>
-      <c r="AF14">
+      <c r="AF14" s="1">
         <v>2.3994479883633673e-07</v>
       </c>
-      <c r="AG14">
+      <c r="AG14" s="1">
         <v>5.0847314204464336e-07</v>
       </c>
-      <c r="AH14">
+      <c r="AH14" s="1">
         <v>2.8606393510425773e-07</v>
       </c>
-      <c r="AI14">
+      <c r="AI14" s="1">
         <v>-2.0498787930709806e-07</v>
       </c>
-      <c r="AJ14">
+      <c r="AJ14" s="1">
         <v>-0.00047432476289304792</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15">
+        <v>42</v>
+      </c>
+      <c r="B15" s="1">
         <v>-1.6804323362127245</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>-0.00010878091798493191</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>5.7311346521620054e-05</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>-7.7023771389335216e-07</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>0.017568890842684808</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>-0.0025586528642843327</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>0.00026010877247331085</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>7.1817749711419743e-05</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>-2.3579531706637614e-05</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>0.0002903713749994475</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>-5.8810712924420841e-05</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <v>-4.92187563628744e-05</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <v>-0.0070759917537936085</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="1">
         <v>-1.2313822634882186e-05</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="1">
         <v>1.1952489193675031</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="1">
         <v>0.69283125051929706</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="1">
         <v>0.71433755521899811</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="1">
         <v>0.71335681114590277</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="1">
         <v>-2.8175447173123258e-05</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="1">
         <v>0.0013294984176517796</v>
       </c>
-      <c r="V15">
+      <c r="V15" s="1">
         <v>0.70791425329633872</v>
       </c>
-      <c r="W15">
+      <c r="W15" s="1">
         <v>0.70748696170750625</v>
       </c>
-      <c r="X15">
+      <c r="X15" s="1">
         <v>0.70755732615003963</v>
       </c>
-      <c r="Y15">
+      <c r="Y15" s="1">
         <v>0.0027068519761707655</v>
       </c>
-      <c r="Z15">
+      <c r="Z15" s="1">
         <v>0.001034271566945133</v>
       </c>
-      <c r="AA15">
+      <c r="AA15" s="1">
         <v>0.001710319448412212</v>
       </c>
-      <c r="AB15">
+      <c r="AB15" s="1">
         <v>-0.00072880693295338667</v>
       </c>
-      <c r="AC15">
+      <c r="AC15" s="1">
         <v>-0.00010227369030904598</v>
       </c>
-      <c r="AD15">
+      <c r="AD15" s="1">
         <v>0.0050700265612909634</v>
       </c>
-      <c r="AE15">
+      <c r="AE15" s="1">
         <v>0.0010377078866654621</v>
       </c>
-      <c r="AF15">
+      <c r="AF15" s="1">
         <v>0.00071030591685222744</v>
       </c>
-      <c r="AG15">
+      <c r="AG15" s="1">
         <v>0.0010502261299347726</v>
       </c>
-      <c r="AH15">
+      <c r="AH15" s="1">
         <v>0.00053820313139241183</v>
       </c>
-      <c r="AI15">
+      <c r="AI15" s="1">
         <v>-0.00011393515887328509</v>
       </c>
-      <c r="AJ15">
+      <c r="AJ15" s="1">
         <v>-0.70866197560460176</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16">
+        <v>43</v>
+      </c>
+      <c r="B16" s="1">
         <v>-2.5405915568087774</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>-0.00026238988266270874</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>0.00010994771497474394</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>-1.3228938614973889e-06</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>0.017679513365496499</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>0.00055079472599313861</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>-0.00095032267962347509</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>0.00011162383090374971</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>-3.8269578004178498e-05</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>0.00013432930131396757</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>-3.1060536800473054e-05</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="1">
         <v>4.8331764270175233e-06</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="1">
         <v>0.00012921222998098138</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="1">
         <v>-6.9409438370631528e-05</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="1">
         <v>0.69283125051929706</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="1">
         <v>0.93723394750738098</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="1">
         <v>0.77066282575034784</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="1">
         <v>0.77102914537067224</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="1">
         <v>-0.0029724899112242853</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="1">
         <v>0.0015499009350927705</v>
       </c>
-      <c r="V16">
+      <c r="V16" s="1">
         <v>0.74417608074757757</v>
       </c>
-      <c r="W16">
+      <c r="W16" s="1">
         <v>0.74438346941918243</v>
       </c>
-      <c r="X16">
+      <c r="X16" s="1">
         <v>0.74429792025226449</v>
       </c>
-      <c r="Y16">
+      <c r="Y16" s="1">
         <v>0.002038612932761856</v>
       </c>
-      <c r="Z16">
+      <c r="Z16" s="1">
         <v>-0.00021060822542229296</v>
       </c>
-      <c r="AA16">
+      <c r="AA16" s="1">
         <v>0.00082800659853160541</v>
       </c>
-      <c r="AB16">
+      <c r="AB16" s="1">
         <v>-0.00082734463075938292</v>
       </c>
-      <c r="AC16">
+      <c r="AC16" s="1">
         <v>-0.00020470133485611663</v>
       </c>
-      <c r="AD16">
+      <c r="AD16" s="1">
         <v>0.0052484460646281539</v>
       </c>
-      <c r="AE16">
+      <c r="AE16" s="1">
         <v>0.00089441608655860261</v>
       </c>
-      <c r="AF16">
+      <c r="AF16" s="1">
         <v>0.00012729077998352434</v>
       </c>
-      <c r="AG16">
+      <c r="AG16" s="1">
         <v>0.0011976764371556259</v>
       </c>
-      <c r="AH16">
+      <c r="AH16" s="1">
         <v>-9.468572262855135e-05</v>
       </c>
-      <c r="AI16">
+      <c r="AI16" s="1">
         <v>-7.3055139630642807e-05</v>
       </c>
-      <c r="AJ16">
+      <c r="AJ16" s="1">
         <v>-0.74579518558071944</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17">
+        <v>44</v>
+      </c>
+      <c r="B17" s="1">
         <v>-2.5966669642460136</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>-9.0261108637345222e-05</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>2.6836925680571663e-05</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>-7.2131062553502718e-07</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>0.018943872478959987</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>0.0016005818980460483</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>0.0011109213906710521</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>-0.00070125748488011343</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <v>-4.6463884831110785e-05</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>0.00013455033009500622</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="1">
         <v>-4.5534078948732888e-06</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="1">
         <v>-5.7343848907391074e-05</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="1">
         <v>-0.002717106252101989</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="1">
         <v>-4.7350625022449824e-05</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="1">
         <v>0.71433755521899811</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="1">
         <v>0.77066282575034784</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="1">
         <v>0.79827428473330841</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="1">
         <v>0.77450084980314804</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="1">
         <v>-0.0031738887611559852</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="1">
         <v>0.0021458651427191007</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="1">
         <v>0.75183612397660093</v>
       </c>
-      <c r="W17">
+      <c r="W17" s="1">
         <v>0.75243540590947044</v>
       </c>
-      <c r="X17">
+      <c r="X17" s="1">
         <v>0.75249214717773993</v>
       </c>
-      <c r="Y17">
+      <c r="Y17" s="1">
         <v>0.00042360982084715948</v>
       </c>
-      <c r="Z17">
+      <c r="Z17" s="1">
         <v>-0.00031433576740405589</v>
       </c>
-      <c r="AA17">
+      <c r="AA17" s="1">
         <v>0.00071805760428844678</v>
       </c>
-      <c r="AB17">
+      <c r="AB17" s="1">
         <v>-0.00043872925190580753</v>
       </c>
-      <c r="AC17">
+      <c r="AC17" s="1">
         <v>-0.00056491011687828663</v>
       </c>
-      <c r="AD17">
+      <c r="AD17" s="1">
         <v>0.0065579347271622623</v>
       </c>
-      <c r="AE17">
+      <c r="AE17" s="1">
         <v>0.0011885060127039271</v>
       </c>
-      <c r="AF17">
+      <c r="AF17" s="1">
         <v>0.00031737489451599821</v>
       </c>
-      <c r="AG17">
+      <c r="AG17" s="1">
         <v>0.0012324113330018927</v>
       </c>
-      <c r="AH17">
+      <c r="AH17" s="1">
         <v>0.00043938872795945549</v>
       </c>
-      <c r="AI17">
+      <c r="AI17" s="1">
         <v>-2.4431924458487297e-05</v>
       </c>
-      <c r="AJ17">
+      <c r="AJ17" s="1">
         <v>-0.75293696522668818</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18">
+        <v>45</v>
+      </c>
+      <c r="B18" s="1">
         <v>-2.5936255248109625</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>0.00013666374996979032</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>-8.9927143420649497e-05</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>2.008934254197254e-07</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>0.022204879403266667</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>0.0048727796495035263</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>0.0043375047181439755</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>0.0030730265186940612</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="1">
         <v>-0.00014952514504657438</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>0.00010753582804176555</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <v>1.9871520390568826e-05</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="1">
         <v>4.1875175672900111e-05</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="1">
         <v>-0.0032864514040665781</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="1">
         <v>-4.6332056702456508e-05</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="1">
         <v>0.71335681114590277</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="1">
         <v>0.77102914537067224</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="1">
         <v>0.77450084980314804</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="1">
         <v>0.79245061775539316</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="1">
         <v>-0.0015426331037102226</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="1">
         <v>-0.001786567050606213</v>
       </c>
-      <c r="V18">
+      <c r="V18" s="1">
         <v>0.75330519502875881</v>
       </c>
-      <c r="W18">
+      <c r="W18" s="1">
         <v>0.75380263457930119</v>
       </c>
-      <c r="X18">
+      <c r="X18" s="1">
         <v>0.7542096633819052</v>
       </c>
-      <c r="Y18">
+      <c r="Y18" s="1">
         <v>0.00047442248791101926</v>
       </c>
-      <c r="Z18">
+      <c r="Z18" s="1">
         <v>-0.00023680040731779983</v>
       </c>
-      <c r="AA18">
+      <c r="AA18" s="1">
         <v>0.00075625434442305739</v>
       </c>
-      <c r="AB18">
+      <c r="AB18" s="1">
         <v>-0.0003996768965324124</v>
       </c>
-      <c r="AC18">
+      <c r="AC18" s="1">
         <v>-0.00064093912126514385</v>
       </c>
-      <c r="AD18">
+      <c r="AD18" s="1">
         <v>0.0060686167833488014</v>
       </c>
-      <c r="AE18">
+      <c r="AE18" s="1">
         <v>0.00073431832107828665</v>
       </c>
-      <c r="AF18">
+      <c r="AF18" s="1">
         <v>0.00014897019524806598</v>
       </c>
-      <c r="AG18">
+      <c r="AG18" s="1">
         <v>0.0012494126615120171</v>
       </c>
-      <c r="AH18">
+      <c r="AH18" s="1">
         <v>0.00030299708893311017</v>
       </c>
-      <c r="AI18">
+      <c r="AI18" s="1">
         <v>-8.9176985475641901e-06</v>
       </c>
-      <c r="AJ18">
+      <c r="AJ18" s="1">
         <v>-0.75433967873682439</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19">
+        <v>46</v>
+      </c>
+      <c r="B19" s="1">
         <v>0.16762755212183331</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>6.4827808928310161e-06</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>-1.0564010437967523e-05</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>1.1535814464094304e-07</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>0.00011424295502333133</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>5.9901328818335957e-05</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>7.3125986406844147e-05</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>4.6637510778960178e-05</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>-0.00017319083128352944</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>1.7320979083480879e-05</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>-5.3462092672487571e-06</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="1">
         <v>8.4159432628448208e-05</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="1">
         <v>-0.0011954039098147149</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="1">
         <v>-4.9277919397303619e-06</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="1">
         <v>-2.8175447173123258e-05</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="1">
         <v>-0.0029724899112242853</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="1">
         <v>-0.0031738887611559852</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="1">
         <v>-0.0015426331037102226</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="1">
         <v>0.0046084295786780645</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="1">
         <v>-0.0027562292747556243</v>
       </c>
-      <c r="V19">
+      <c r="V19" s="1">
         <v>-0.0018902109745542119</v>
       </c>
-      <c r="W19">
+      <c r="W19" s="1">
         <v>-0.0018124902242243905</v>
       </c>
-      <c r="X19">
+      <c r="X19" s="1">
         <v>-0.0017998589346280424</v>
       </c>
-      <c r="Y19">
+      <c r="Y19" s="1">
         <v>0.00010302689237393734</v>
       </c>
-      <c r="Z19">
+      <c r="Z19" s="1">
         <v>0.00014803821161096654</v>
       </c>
-      <c r="AA19">
+      <c r="AA19" s="1">
         <v>0.00012031478483575297</v>
       </c>
-      <c r="AB19">
+      <c r="AB19" s="1">
         <v>0.00010847514894948845</v>
       </c>
-      <c r="AC19">
+      <c r="AC19" s="1">
         <v>-7.6914877208255174e-05</v>
       </c>
-      <c r="AD19">
+      <c r="AD19" s="1">
         <v>0.00025129422109751421</v>
       </c>
-      <c r="AE19">
+      <c r="AE19" s="1">
         <v>-9.8776831141167464e-06</v>
       </c>
-      <c r="AF19">
+      <c r="AF19" s="1">
         <v>2.460618396536272e-05</v>
       </c>
-      <c r="AG19">
+      <c r="AG19" s="1">
         <v>-9.5243304870931515e-05</v>
       </c>
-      <c r="AH19">
+      <c r="AH19" s="1">
         <v>-3.8673588672727128e-06</v>
       </c>
-      <c r="AI19">
+      <c r="AI19" s="1">
         <v>-4.3407197007044439e-06</v>
       </c>
-      <c r="AJ19">
+      <c r="AJ19" s="1">
         <v>0.0020266660619707036</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20">
+        <v>47</v>
+      </c>
+      <c r="B20" s="1">
         <v>-0.035243613630204798</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>-1.9362708076021975e-05</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>4.8689167075449156e-06</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>-3.5064294631734573e-08</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>-4.179482706608245e-05</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>-4.9047598135670604e-05</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>-5.2713071737930722e-05</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>-5.9330133662844352e-05</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>0.00013134303715893689</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>2.4349663944748064e-05</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>-8.7497160120588158e-06</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="1">
         <v>-0.00023382115944873489</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="1">
         <v>-0.00098085062576415785</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="1">
         <v>-2.4536933050857528e-05</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="1">
         <v>0.0013294984176517796</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="1">
         <v>0.0015499009350927705</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="1">
         <v>0.0021458651427191007</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="1">
         <v>-0.001786567050606213</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="1">
         <v>-0.0027562292747556243</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="1">
         <v>0.0087203363828420935</v>
       </c>
-      <c r="V20">
+      <c r="V20" s="1">
         <v>-0.0094878629847446917</v>
       </c>
-      <c r="W20">
+      <c r="W20" s="1">
         <v>-0.0093614058497291722</v>
       </c>
-      <c r="X20">
+      <c r="X20" s="1">
         <v>-0.0094308092756818836</v>
       </c>
-      <c r="Y20">
+      <c r="Y20" s="1">
         <v>4.3360038991907296e-05</v>
       </c>
-      <c r="Z20">
+      <c r="Z20" s="1">
         <v>8.6003488357058971e-05</v>
       </c>
-      <c r="AA20">
+      <c r="AA20" s="1">
         <v>4.9191436812952858e-05</v>
       </c>
-      <c r="AB20">
+      <c r="AB20" s="1">
         <v>8.5586428853287751e-06</v>
       </c>
-      <c r="AC20">
+      <c r="AC20" s="1">
         <v>9.1252196393017842e-05</v>
       </c>
-      <c r="AD20">
+      <c r="AD20" s="1">
         <v>-2.9445214180903387e-05</v>
       </c>
-      <c r="AE20">
+      <c r="AE20" s="1">
         <v>-0.00013317301409234653</v>
       </c>
-      <c r="AF20">
+      <c r="AF20" s="1">
         <v>-3.3719372790186179e-05</v>
       </c>
-      <c r="AG20">
+      <c r="AG20" s="1">
         <v>5.1080740723754691e-05</v>
       </c>
-      <c r="AH20">
+      <c r="AH20" s="1">
         <v>-8.7232181652158397e-05</v>
       </c>
-      <c r="AI20">
+      <c r="AI20" s="1">
         <v>3.3292910232073179e-06</v>
       </c>
-      <c r="AJ20">
+      <c r="AJ20" s="1">
         <v>0.0092554569361103511</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21">
+        <v>48</v>
+      </c>
+      <c r="B21" s="1">
         <v>-2.6209011430250375</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>-0.00034370944801096669</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>-0.0005397535906132339</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>4.5020594267030065e-06</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>0.021069959305103893</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>0.0035966297823325369</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>0.0033084991486582675</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="1">
         <v>0.0013563238640281455</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="1">
         <v>-0.0004038364205639807</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>0.000237833754587246</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="1">
         <v>5.3609801850538341e-05</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="1">
         <v>0.00016874927418075269</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="1">
         <v>0.013588647030462395</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="1">
         <v>0.00050901928451731432</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="1">
         <v>0.70791425329633872</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="1">
         <v>0.74417608074757757</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="1">
         <v>0.75183612397660093</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="1">
         <v>0.75330519502875881</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="1">
         <v>-0.0018902109745542119</v>
       </c>
-      <c r="U21">
+      <c r="U21" s="1">
         <v>-0.0094878629847446917</v>
       </c>
-      <c r="V21">
+      <c r="V21" s="1">
         <v>0.96901139070018916</v>
       </c>
-      <c r="W21">
+      <c r="W21" s="1">
         <v>0.9680188219458985</v>
       </c>
-      <c r="X21">
+      <c r="X21" s="1">
         <v>0.96854835509334714</v>
       </c>
-      <c r="Y21">
+      <c r="Y21" s="1">
         <v>0.0062492391487265</v>
       </c>
-      <c r="Z21">
+      <c r="Z21" s="1">
         <v>0.00096130749677023064</v>
       </c>
-      <c r="AA21">
+      <c r="AA21" s="1">
         <v>0.0013500206872852361</v>
       </c>
-      <c r="AB21">
+      <c r="AB21" s="1">
         <v>0.00034766283270958043</v>
       </c>
-      <c r="AC21">
+      <c r="AC21" s="1">
         <v>-0.0033508816495628757</v>
       </c>
-      <c r="AD21">
+      <c r="AD21" s="1">
         <v>0.0067799304749120992</v>
       </c>
-      <c r="AE21">
+      <c r="AE21" s="1">
         <v>0.001807649983161963</v>
       </c>
-      <c r="AF21">
+      <c r="AF21" s="1">
         <v>4.8711928572697794e-05</v>
       </c>
-      <c r="AG21">
+      <c r="AG21" s="1">
         <v>0.0010070784718125836</v>
       </c>
-      <c r="AH21">
+      <c r="AH21" s="1">
         <v>0.00030001005084773213</v>
       </c>
-      <c r="AI21">
+      <c r="AI21" s="1">
         <v>-9.4805823445676118e-05</v>
       </c>
-      <c r="AJ21">
+      <c r="AJ21" s="1">
         <v>-0.95596920904121663</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22">
+        <v>49</v>
+      </c>
+      <c r="B22" s="1">
         <v>-2.7959587756199955</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>-0.00038123850361427262</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>-0.0006404350434870362</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>5.7596146379166823e-06</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <v>0.021668429543554701</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>0.0043258832201138993</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>0.0037497640668845544</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="1">
         <v>0.0015397498999126927</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="1">
         <v>-0.00043605887568286695</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>0.00020429692557313444</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="1">
         <v>1.3378334471041314e-05</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="1">
         <v>0.00015401825424141388</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="1">
         <v>0.01372108754692636</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="1">
         <v>0.00050929086983935367</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="1">
         <v>0.70748696170750625</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="1">
         <v>0.74438346941918243</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="1">
         <v>0.75243540590947044</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="1">
         <v>0.75380263457930119</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="1">
         <v>-0.0018124902242243905</v>
       </c>
-      <c r="U22">
+      <c r="U22" s="1">
         <v>-0.0093614058497291722</v>
       </c>
-      <c r="V22">
+      <c r="V22" s="1">
         <v>0.9680188219458985</v>
       </c>
-      <c r="W22">
+      <c r="W22" s="1">
         <v>0.97069082092233361</v>
       </c>
-      <c r="X22">
+      <c r="X22" s="1">
         <v>0.97076518148039237</v>
       </c>
-      <c r="Y22">
+      <c r="Y22" s="1">
         <v>0.0070773160081516531</v>
       </c>
-      <c r="Z22">
+      <c r="Z22" s="1">
         <v>0.00056338954362339377</v>
       </c>
-      <c r="AA22">
+      <c r="AA22" s="1">
         <v>0.00074582708932707797</v>
       </c>
-      <c r="AB22">
+      <c r="AB22" s="1">
         <v>0.00061316038920194299</v>
       </c>
-      <c r="AC22">
+      <c r="AC22" s="1">
         <v>-0.0033609167410865171</v>
       </c>
-      <c r="AD22">
+      <c r="AD22" s="1">
         <v>0.0069676816021957411</v>
       </c>
-      <c r="AE22">
+      <c r="AE22" s="1">
         <v>0.0018612265220665503</v>
       </c>
-      <c r="AF22">
+      <c r="AF22" s="1">
         <v>-1.7251585331279351e-05</v>
       </c>
-      <c r="AG22">
+      <c r="AG22" s="1">
         <v>0.001063323350324441</v>
       </c>
-      <c r="AH22">
+      <c r="AH22" s="1">
         <v>0.00039969706077941369</v>
       </c>
-      <c r="AI22">
+      <c r="AI22" s="1">
         <v>-0.00010860416903446524</v>
       </c>
-      <c r="AJ22">
+      <c r="AJ22" s="1">
         <v>-0.95602778939077449</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23">
+        <v>50</v>
+      </c>
+      <c r="B23" s="1">
         <v>-2.6677125365464915</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="1">
         <v>0.00010111795208044614</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="1">
         <v>-0.00062437417118981332</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="1">
         <v>5.6402864548445454e-06</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="1">
         <v>0.02199071377853621</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <v>0.0046071574782358907</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>0.0042417885180778808</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="1">
         <v>0.001846139727709119</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="1">
         <v>-0.00046525441437811436</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="1">
         <v>-0.00050355549718590653</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="1">
         <v>-2.4191708849444521e-05</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="1">
         <v>0.00021753172117052014</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="1">
         <v>0.013264811887667771</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="1">
         <v>0.00051089160135695932</v>
       </c>
-      <c r="P23">
+      <c r="P23" s="1">
         <v>0.70755732615003963</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="1">
         <v>0.74429792025226449</v>
       </c>
-      <c r="R23">
+      <c r="R23" s="1">
         <v>0.75249214717773993</v>
       </c>
-      <c r="S23">
+      <c r="S23" s="1">
         <v>0.7542096633819052</v>
       </c>
-      <c r="T23">
+      <c r="T23" s="1">
         <v>-0.0017998589346280424</v>
       </c>
-      <c r="U23">
+      <c r="U23" s="1">
         <v>-0.0094308092756818836</v>
       </c>
-      <c r="V23">
+      <c r="V23" s="1">
         <v>0.96854835509334714</v>
       </c>
-      <c r="W23">
+      <c r="W23" s="1">
         <v>0.97076518148039237</v>
       </c>
-      <c r="X23">
+      <c r="X23" s="1">
         <v>0.97380801704636655</v>
       </c>
-      <c r="Y23">
+      <c r="Y23" s="1">
         <v>0.0026800938051496845</v>
       </c>
-      <c r="Z23">
+      <c r="Z23" s="1">
         <v>-0.0039704952397188187</v>
       </c>
-      <c r="AA23">
+      <c r="AA23" s="1">
         <v>-0.004138346095874823</v>
       </c>
-      <c r="AB23">
+      <c r="AB23" s="1">
         <v>0.00069408457760096465</v>
       </c>
-      <c r="AC23">
+      <c r="AC23" s="1">
         <v>-0.0034924115215028417</v>
       </c>
-      <c r="AD23">
+      <c r="AD23" s="1">
         <v>0.0069969822786748459</v>
       </c>
-      <c r="AE23">
+      <c r="AE23" s="1">
         <v>0.0019557889576951037</v>
       </c>
-      <c r="AF23">
+      <c r="AF23" s="1">
         <v>-4.710165807966793e-05</v>
       </c>
-      <c r="AG23">
+      <c r="AG23" s="1">
         <v>0.0010840283227032677</v>
       </c>
-      <c r="AH23">
+      <c r="AH23" s="1">
         <v>0.0003755324623292422</v>
       </c>
-      <c r="AI23">
+      <c r="AI23" s="1">
         <v>-0.00012355707058292476</v>
       </c>
-      <c r="AJ23">
+      <c r="AJ23" s="1">
         <v>-0.95256900919423559</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24">
+        <v>51</v>
+      </c>
+      <c r="B24" s="1">
         <v>1.2213625154313736</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="1">
         <v>-0.0018928150107869581</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="1">
         <v>0.00024117800619271573</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>-1.9889607057155336e-06</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="1">
         <v>0.00032035733632116456</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="1">
         <v>0.00027646246758786073</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>0.0007381263736963257</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="1">
         <v>0.0006309764368931099</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="1">
         <v>-0.00010913946944126323</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="1">
         <v>0.014062837341612913</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="1">
         <v>-0.00018906383220897632</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="1">
         <v>-9.1862754256928625e-05</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="1">
         <v>0.0029928128904984663</v>
       </c>
-      <c r="O24">
+      <c r="O24" s="1">
         <v>-1.5100629061880676e-05</v>
       </c>
-      <c r="P24">
+      <c r="P24" s="1">
         <v>0.0027068519761707655</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="1">
         <v>0.002038612932761856</v>
       </c>
-      <c r="R24">
+      <c r="R24" s="1">
         <v>0.00042360982084715948</v>
       </c>
-      <c r="S24">
+      <c r="S24" s="1">
         <v>0.00047442248791101926</v>
       </c>
-      <c r="T24">
+      <c r="T24" s="1">
         <v>0.00010302689237393734</v>
       </c>
-      <c r="U24">
+      <c r="U24" s="1">
         <v>4.3360038991907296e-05</v>
       </c>
-      <c r="V24">
+      <c r="V24" s="1">
         <v>0.0062492391487265</v>
       </c>
-      <c r="W24">
+      <c r="W24" s="1">
         <v>0.0070773160081516531</v>
       </c>
-      <c r="X24">
+      <c r="X24" s="1">
         <v>0.0026800938051496845</v>
       </c>
-      <c r="Y24">
+      <c r="Y24" s="1">
         <v>0.11274302572694185</v>
       </c>
-      <c r="Z24">
+      <c r="Z24" s="1">
         <v>0.10030837014605504</v>
       </c>
-      <c r="AA24">
+      <c r="AA24" s="1">
         <v>0.099529352589697556</v>
       </c>
-      <c r="AB24">
+      <c r="AB24" s="1">
         <v>-0.00059007730513594347</v>
       </c>
-      <c r="AC24">
+      <c r="AC24" s="1">
         <v>-0.00011010965264570891</v>
       </c>
-      <c r="AD24">
+      <c r="AD24" s="1">
         <v>-9.5171997103238315e-05</v>
       </c>
-      <c r="AE24">
+      <c r="AE24" s="1">
         <v>-3.9541354336584955e-05</v>
       </c>
-      <c r="AF24">
+      <c r="AF24" s="1">
         <v>5.8062539077596148e-05</v>
       </c>
-      <c r="AG24">
+      <c r="AG24" s="1">
         <v>3.9922894881645743e-05</v>
       </c>
-      <c r="AH24">
+      <c r="AH24" s="1">
         <v>-0.00020530490894841644</v>
       </c>
-      <c r="AI24">
+      <c r="AI24" s="1">
         <v>-0.00017755753447758465</v>
       </c>
-      <c r="AJ24">
+      <c r="AJ24" s="1">
         <v>-0.10931535525606169</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25">
+        <v>52</v>
+      </c>
+      <c r="B25" s="1">
         <v>0.65902586320784884</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="1">
         <v>-0.0016495795900745972</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="1">
         <v>-5.081103497035273e-05</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="1">
         <v>2.5873068649291832e-07</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="1">
         <v>-0.0010386763394041828</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="1">
         <v>-0.0007603851459399417</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
         <v>0.00026311029675399496</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="1">
         <v>0.00014071430887927625</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="1">
         <v>-0.00014877135159677404</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="1">
         <v>0.014215474860256046</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="1">
         <v>-0.00019371695188810328</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="1">
         <v>-0.00012078421688511324</v>
       </c>
-      <c r="N25">
+      <c r="N25" s="1">
         <v>0.001481843575664883</v>
       </c>
-      <c r="O25">
+      <c r="O25" s="1">
         <v>-1.7922132219900104e-06</v>
       </c>
-      <c r="P25">
+      <c r="P25" s="1">
         <v>0.001034271566945133</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" s="1">
         <v>-0.00021060822542229296</v>
       </c>
-      <c r="R25">
+      <c r="R25" s="1">
         <v>-0.00031433576740405589</v>
       </c>
-      <c r="S25">
+      <c r="S25" s="1">
         <v>-0.00023680040731779983</v>
       </c>
-      <c r="T25">
+      <c r="T25" s="1">
         <v>0.00014803821161096654</v>
       </c>
-      <c r="U25">
+      <c r="U25" s="1">
         <v>8.6003488357058971e-05</v>
       </c>
-      <c r="V25">
+      <c r="V25" s="1">
         <v>0.00096130749677023064</v>
       </c>
-      <c r="W25">
+      <c r="W25" s="1">
         <v>0.00056338954362339377</v>
       </c>
-      <c r="X25">
+      <c r="X25" s="1">
         <v>-0.0039704952397188187</v>
       </c>
-      <c r="Y25">
+      <c r="Y25" s="1">
         <v>0.10030837014605504</v>
       </c>
-      <c r="Z25">
+      <c r="Z25" s="1">
         <v>0.10307268588919444</v>
       </c>
-      <c r="AA25">
+      <c r="AA25" s="1">
         <v>0.10134403756203375</v>
       </c>
-      <c r="AB25">
+      <c r="AB25" s="1">
         <v>-0.001433194932616076</v>
       </c>
-      <c r="AC25">
+      <c r="AC25" s="1">
         <v>-0.00029862619618380246</v>
       </c>
-      <c r="AD25">
+      <c r="AD25" s="1">
         <v>0.00019604129095138201</v>
       </c>
-      <c r="AE25">
+      <c r="AE25" s="1">
         <v>0.00010339867296786653</v>
       </c>
-      <c r="AF25">
+      <c r="AF25" s="1">
         <v>0.00061086858273329443</v>
       </c>
-      <c r="AG25">
+      <c r="AG25" s="1">
         <v>0.00026213878349254718</v>
       </c>
-      <c r="AH25">
+      <c r="AH25" s="1">
         <v>2.3607548957658986e-05</v>
       </c>
-      <c r="AI25">
+      <c r="AI25" s="1">
         <v>-0.00016395808673495046</v>
       </c>
-      <c r="AJ25">
+      <c r="AJ25" s="1">
         <v>-0.095520386018529649</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26">
+        <v>53</v>
+      </c>
+      <c r="B26" s="1">
         <v>0.40887148844633114</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="1">
         <v>-0.0016200699795548121</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="1">
         <v>8.4966693270198233e-05</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="1">
         <v>-2.056708152937929e-06</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="1">
         <v>-0.00026096601753147503</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="1">
         <v>-0.00026942867940675573</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>0.00028401935120043678</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="1">
         <v>0.00010749732504297319</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="1">
         <v>-0.00013475057093880635</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="1">
         <v>0.014151921554778792</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="1">
         <v>-0.0001074363380637266</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="1">
         <v>-9.3792284166807245e-05</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="1">
         <v>0.0014790213580939903</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="1">
         <v>-3.3485194414020509e-06</v>
       </c>
-      <c r="P26">
+      <c r="P26" s="1">
         <v>0.001710319448412212</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" s="1">
         <v>0.00082800659853160541</v>
       </c>
-      <c r="R26">
+      <c r="R26" s="1">
         <v>0.00071805760428844678</v>
       </c>
-      <c r="S26">
+      <c r="S26" s="1">
         <v>0.00075625434442305739</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="1">
         <v>0.00012031478483575297</v>
       </c>
-      <c r="U26">
+      <c r="U26" s="1">
         <v>4.9191436812952858e-05</v>
       </c>
-      <c r="V26">
+      <c r="V26" s="1">
         <v>0.0013500206872852361</v>
       </c>
-      <c r="W26">
+      <c r="W26" s="1">
         <v>0.00074582708932707797</v>
       </c>
-      <c r="X26">
+      <c r="X26" s="1">
         <v>-0.004138346095874823</v>
       </c>
-      <c r="Y26">
+      <c r="Y26" s="1">
         <v>0.099529352589697556</v>
       </c>
-      <c r="Z26">
+      <c r="Z26" s="1">
         <v>0.10134403756203375</v>
       </c>
-      <c r="AA26">
+      <c r="AA26" s="1">
         <v>0.10620996900266884</v>
       </c>
-      <c r="AB26">
+      <c r="AB26" s="1">
         <v>-0.0013758626145508998</v>
       </c>
-      <c r="AC26">
+      <c r="AC26" s="1">
         <v>7.6692304151462429e-06</v>
       </c>
-      <c r="AD26">
+      <c r="AD26" s="1">
         <v>0.00064521340018945314</v>
       </c>
-      <c r="AE26">
+      <c r="AE26" s="1">
         <v>0.00021595016025085373</v>
       </c>
-      <c r="AF26">
+      <c r="AF26" s="1">
         <v>0.00064291230122710645</v>
       </c>
-      <c r="AG26">
+      <c r="AG26" s="1">
         <v>0.00043240917989592967</v>
       </c>
-      <c r="AH26">
+      <c r="AH26" s="1">
         <v>0.00010952341722379917</v>
       </c>
-      <c r="AI26">
+      <c r="AI26" s="1">
         <v>-0.00017726224461141974</v>
       </c>
-      <c r="AJ26">
+      <c r="AJ26" s="1">
         <v>-0.097042069255456928</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27">
+        <v>54</v>
+      </c>
+      <c r="B27" s="1">
         <v>0.14332748777184942</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="1">
         <v>0.00024103573777695759</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="1">
         <v>6.8899636296232181e-05</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="1">
         <v>-3.4340088257294334e-07</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="1">
         <v>-1.4058278600929388e-05</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="1">
         <v>4.0004103937288862e-05</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>0.00025190342250615131</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="1">
         <v>3.351913522857869e-05</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="1">
         <v>-1.4556045232093979e-05</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="1">
         <v>-0.00022320505019344351</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="1">
         <v>-2.4904729257543503e-05</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="1">
         <v>-1.5419250900175327e-05</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="1">
         <v>-0.00025598036844772865</v>
       </c>
-      <c r="O27">
+      <c r="O27" s="1">
         <v>2.5329416967349277e-06</v>
       </c>
-      <c r="P27">
+      <c r="P27" s="1">
         <v>-0.00072880693295338667</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" s="1">
         <v>-0.00082734463075938292</v>
       </c>
-      <c r="R27">
+      <c r="R27" s="1">
         <v>-0.00043872925190580753</v>
       </c>
-      <c r="S27">
+      <c r="S27" s="1">
         <v>-0.0003996768965324124</v>
       </c>
-      <c r="T27">
+      <c r="T27" s="1">
         <v>0.00010847514894948845</v>
       </c>
-      <c r="U27">
+      <c r="U27" s="1">
         <v>8.5586428853287751e-06</v>
       </c>
-      <c r="V27">
+      <c r="V27" s="1">
         <v>0.00034766283270958043</v>
       </c>
-      <c r="W27">
+      <c r="W27" s="1">
         <v>0.00061316038920194299</v>
       </c>
-      <c r="X27">
+      <c r="X27" s="1">
         <v>0.00069408457760096465</v>
       </c>
-      <c r="Y27">
+      <c r="Y27" s="1">
         <v>-0.00059007730513594347</v>
       </c>
-      <c r="Z27">
+      <c r="Z27" s="1">
         <v>-0.001433194932616076</v>
       </c>
-      <c r="AA27">
+      <c r="AA27" s="1">
         <v>-0.0013758626145508998</v>
       </c>
-      <c r="AB27">
+      <c r="AB27" s="1">
         <v>0.0031796096117264775</v>
       </c>
-      <c r="AC27">
+      <c r="AC27" s="1">
         <v>0.0014859868121127437</v>
       </c>
-      <c r="AD27">
+      <c r="AD27" s="1">
         <v>0.0019872777095785812</v>
       </c>
-      <c r="AE27">
+      <c r="AE27" s="1">
         <v>-1.1434733145317729e-05</v>
       </c>
-      <c r="AF27">
+      <c r="AF27" s="1">
         <v>-8.5872892437626424e-05</v>
       </c>
-      <c r="AG27">
+      <c r="AG27" s="1">
         <v>-2.2295642024893403e-05</v>
       </c>
-      <c r="AH27">
+      <c r="AH27" s="1">
         <v>1.8459878584561841e-05</v>
       </c>
-      <c r="AI27">
+      <c r="AI27" s="1">
         <v>9.7761127252276399e-06</v>
       </c>
-      <c r="AJ27">
+      <c r="AJ27" s="1">
         <v>-0.0032743294009943587</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28">
+        <v>55</v>
+      </c>
+      <c r="B28" s="1">
         <v>-0.1165197482272549</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="1">
         <v>0.00011924923375726782</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="1">
         <v>0.00017327627778686224</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="1">
         <v>-1.5473365537425886e-06</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="1">
         <v>-0.00049573150907209537</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="1">
         <v>-0.00028275442142084491</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>-4.8813587765730328e-05</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="1">
         <v>-4.8870536680912071e-06</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="1">
         <v>-2.239016202774116e-05</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="1">
         <v>-4.0828430524779261e-05</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="1">
         <v>2.4589708721563788e-05</v>
       </c>
-      <c r="M28">
+      <c r="M28" s="1">
         <v>-5.8223042586120226e-05</v>
       </c>
-      <c r="N28">
+      <c r="N28" s="1">
         <v>-1.1142196836181045e-05</v>
       </c>
-      <c r="O28">
+      <c r="O28" s="1">
         <v>-6.7862380130840943e-06</v>
       </c>
-      <c r="P28">
+      <c r="P28" s="1">
         <v>-0.00010227369030904598</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" s="1">
         <v>-0.00020470133485611663</v>
       </c>
-      <c r="R28">
+      <c r="R28" s="1">
         <v>-0.00056491011687828663</v>
       </c>
-      <c r="S28">
+      <c r="S28" s="1">
         <v>-0.00064093912126514385</v>
       </c>
-      <c r="T28">
+      <c r="T28" s="1">
         <v>-7.6914877208255174e-05</v>
       </c>
-      <c r="U28">
+      <c r="U28" s="1">
         <v>9.1252196393017842e-05</v>
       </c>
-      <c r="V28">
+      <c r="V28" s="1">
         <v>-0.0033508816495628757</v>
       </c>
-      <c r="W28">
+      <c r="W28" s="1">
         <v>-0.0033609167410865171</v>
       </c>
-      <c r="X28">
+      <c r="X28" s="1">
         <v>-0.0034924115215028417</v>
       </c>
-      <c r="Y28">
+      <c r="Y28" s="1">
         <v>-0.00011010965264570891</v>
       </c>
-      <c r="Z28">
+      <c r="Z28" s="1">
         <v>-0.00029862619618380246</v>
       </c>
-      <c r="AA28">
+      <c r="AA28" s="1">
         <v>7.6692304151462429e-06</v>
       </c>
-      <c r="AB28">
+      <c r="AB28" s="1">
         <v>0.0014859868121127437</v>
       </c>
-      <c r="AC28">
+      <c r="AC28" s="1">
         <v>0.0030617120829161699</v>
       </c>
-      <c r="AD28">
+      <c r="AD28" s="1">
         <v>0.0017188643101436433</v>
       </c>
-      <c r="AE28">
+      <c r="AE28" s="1">
         <v>-7.9182582058405504e-05</v>
       </c>
-      <c r="AF28">
+      <c r="AF28" s="1">
         <v>-0.00020080040443599189</v>
       </c>
-      <c r="AG28">
+      <c r="AG28" s="1">
         <v>-0.00021169311677380698</v>
       </c>
-      <c r="AH28">
+      <c r="AH28" s="1">
         <v>-9.2808848901034099e-05</v>
       </c>
-      <c r="AI28">
+      <c r="AI28" s="1">
         <v>6.4212969890078476e-06</v>
       </c>
-      <c r="AJ28">
+      <c r="AJ28" s="1">
         <v>-0.0021239170953026316</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29">
+        <v>56</v>
+      </c>
+      <c r="B29" s="1">
         <v>1.3221404696125998</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="1">
         <v>0.00068840872744593655</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="1">
         <v>0.00010350706027987834</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="1">
         <v>-6.6043267596729649e-07</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="1">
         <v>-0.00072073311233299825</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="1">
         <v>-0.00041773354159801816</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>-0.00042193905191306497</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="1">
         <v>-0.00044403147016587222</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="1">
         <v>-4.2531026579442433e-05</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="1">
         <v>-2.0518222535116388e-05</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="1">
         <v>5.5029753541514097e-05</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="1">
         <v>-5.0383729666441494e-05</v>
       </c>
-      <c r="N29">
+      <c r="N29" s="1">
         <v>-0.00090919513640622986</v>
       </c>
-      <c r="O29">
+      <c r="O29" s="1">
         <v>4.842852267768178e-06</v>
       </c>
-      <c r="P29">
+      <c r="P29" s="1">
         <v>0.0050700265612909634</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" s="1">
         <v>0.0052484460646281539</v>
       </c>
-      <c r="R29">
+      <c r="R29" s="1">
         <v>0.0065579347271622623</v>
       </c>
-      <c r="S29">
+      <c r="S29" s="1">
         <v>0.0060686167833488014</v>
       </c>
-      <c r="T29">
+      <c r="T29" s="1">
         <v>0.00025129422109751421</v>
       </c>
-      <c r="U29">
+      <c r="U29" s="1">
         <v>-2.9445214180903387e-05</v>
       </c>
-      <c r="V29">
+      <c r="V29" s="1">
         <v>0.0067799304749120992</v>
       </c>
-      <c r="W29">
+      <c r="W29" s="1">
         <v>0.0069676816021957411</v>
       </c>
-      <c r="X29">
+      <c r="X29" s="1">
         <v>0.0069969822786748459</v>
       </c>
-      <c r="Y29">
+      <c r="Y29" s="1">
         <v>-9.5171997103238315e-05</v>
       </c>
-      <c r="Z29">
+      <c r="Z29" s="1">
         <v>0.00019604129095138201</v>
       </c>
-      <c r="AA29">
+      <c r="AA29" s="1">
         <v>0.00064521340018945314</v>
       </c>
-      <c r="AB29">
+      <c r="AB29" s="1">
         <v>0.0019872777095785812</v>
       </c>
-      <c r="AC29">
+      <c r="AC29" s="1">
         <v>0.0017188643101436433</v>
       </c>
-      <c r="AD29">
+      <c r="AD29" s="1">
         <v>0.016882276212152467</v>
       </c>
-      <c r="AE29">
+      <c r="AE29" s="1">
         <v>-0.00013163313933408846</v>
       </c>
-      <c r="AF29">
+      <c r="AF29" s="1">
         <v>-0.0001675484293951542</v>
       </c>
-      <c r="AG29">
+      <c r="AG29" s="1">
         <v>4.5906587038217588e-05</v>
       </c>
-      <c r="AH29">
+      <c r="AH29" s="1">
         <v>-0.00029558782944295696</v>
       </c>
-      <c r="AI29">
+      <c r="AI29" s="1">
         <v>3.7173032135186159e-05</v>
       </c>
-      <c r="AJ29">
+      <c r="AJ29" s="1">
         <v>-0.012471229429938935</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30">
+        <v>57</v>
+      </c>
+      <c r="B30" s="1">
         <v>-0.076208774108297905</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="1">
         <v>-1.4353810964534732e-05</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="1">
         <v>2.5455467700143824e-05</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="1">
         <v>-2.6496693074220172e-07</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="1">
         <v>-0.00017891261782107364</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="1">
         <v>-0.00020680279456231597</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>-0.00023647467835019023</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="1">
         <v>-0.00018431744315230156</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="1">
         <v>-4.9144655130532115e-05</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="1">
         <v>-1.0812774204390502e-07</v>
       </c>
-      <c r="L30">
+      <c r="L30" s="1">
         <v>7.0147238271235212e-06</v>
       </c>
-      <c r="M30">
+      <c r="M30" s="1">
         <v>2.0333099405035096e-05</v>
       </c>
-      <c r="N30">
+      <c r="N30" s="1">
         <v>0.00054603248295070211</v>
       </c>
-      <c r="O30">
+      <c r="O30" s="1">
         <v>2.6705214604590957e-06</v>
       </c>
-      <c r="P30">
+      <c r="P30" s="1">
         <v>0.0010377078866654621</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" s="1">
         <v>0.00089441608655860261</v>
       </c>
-      <c r="R30">
+      <c r="R30" s="1">
         <v>0.0011885060127039271</v>
       </c>
-      <c r="S30">
+      <c r="S30" s="1">
         <v>0.00073431832107828665</v>
       </c>
-      <c r="T30">
+      <c r="T30" s="1">
         <v>-9.8776831141167464e-06</v>
       </c>
-      <c r="U30">
+      <c r="U30" s="1">
         <v>-0.00013317301409234653</v>
       </c>
-      <c r="V30">
+      <c r="V30" s="1">
         <v>0.001807649983161963</v>
       </c>
-      <c r="W30">
+      <c r="W30" s="1">
         <v>0.0018612265220665503</v>
       </c>
-      <c r="X30">
+      <c r="X30" s="1">
         <v>0.0019557889576951037</v>
       </c>
-      <c r="Y30">
+      <c r="Y30" s="1">
         <v>-3.9541354336584955e-05</v>
       </c>
-      <c r="Z30">
+      <c r="Z30" s="1">
         <v>0.00010339867296786653</v>
       </c>
-      <c r="AA30">
+      <c r="AA30" s="1">
         <v>0.00021595016025085373</v>
       </c>
-      <c r="AB30">
+      <c r="AB30" s="1">
         <v>-1.1434733145317729e-05</v>
       </c>
-      <c r="AC30">
+      <c r="AC30" s="1">
         <v>-7.9182582058405504e-05</v>
       </c>
-      <c r="AD30">
+      <c r="AD30" s="1">
         <v>-0.00013163313933408846</v>
       </c>
-      <c r="AE30">
+      <c r="AE30" s="1">
         <v>0.0044090652512762014</v>
       </c>
-      <c r="AF30">
+      <c r="AF30" s="1">
         <v>0.0023397168933973183</v>
       </c>
-      <c r="AG30">
+      <c r="AG30" s="1">
         <v>0.002346704344400135</v>
       </c>
-      <c r="AH30">
+      <c r="AH30" s="1">
         <v>0.0023553422044259608</v>
       </c>
-      <c r="AI30">
+      <c r="AI30" s="1">
         <v>-8.4817085995199498e-05</v>
       </c>
-      <c r="AJ30">
+      <c r="AJ30" s="1">
         <v>-0.0031902200192739576</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>46</v>
-      </c>
-      <c r="B31">
+        <v>58</v>
+      </c>
+      <c r="B31" s="1">
         <v>0.23650796107064961</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="1">
         <v>5.4969938243985219e-06</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="1">
         <v>-5.0889411249433603e-06</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="1">
         <v>-2.0465625732582261e-08</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="1">
         <v>-0.00021701697311486993</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="1">
         <v>-0.00029414309973394806</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="1">
         <v>-0.0002092715430329441</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="1">
         <v>-0.00019583788490697561</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="1">
         <v>-3.760810596449843e-05</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="1">
         <v>5.2985777610397916e-05</v>
       </c>
-      <c r="L31">
+      <c r="L31" s="1">
         <v>1.7425704554239318e-05</v>
       </c>
-      <c r="M31">
+      <c r="M31" s="1">
         <v>3.2689367787681825e-05</v>
       </c>
-      <c r="N31">
+      <c r="N31" s="1">
         <v>0.00018010415054083451</v>
       </c>
-      <c r="O31">
+      <c r="O31" s="1">
         <v>2.3994479883633673e-07</v>
       </c>
-      <c r="P31">
+      <c r="P31" s="1">
         <v>0.00071030591685222744</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" s="1">
         <v>0.00012729077998352434</v>
       </c>
-      <c r="R31">
+      <c r="R31" s="1">
         <v>0.00031737489451599821</v>
       </c>
-      <c r="S31">
+      <c r="S31" s="1">
         <v>0.00014897019524806598</v>
       </c>
-      <c r="T31">
+      <c r="T31" s="1">
         <v>2.460618396536272e-05</v>
       </c>
-      <c r="U31">
+      <c r="U31" s="1">
         <v>-3.3719372790186179e-05</v>
       </c>
-      <c r="V31">
+      <c r="V31" s="1">
         <v>4.8711928572697794e-05</v>
       </c>
-      <c r="W31">
+      <c r="W31" s="1">
         <v>-1.7251585331279351e-05</v>
       </c>
-      <c r="X31">
+      <c r="X31" s="1">
         <v>-4.710165807966793e-05</v>
       </c>
-      <c r="Y31">
+      <c r="Y31" s="1">
         <v>5.8062539077596148e-05</v>
       </c>
-      <c r="Z31">
+      <c r="Z31" s="1">
         <v>0.00061086858273329443</v>
       </c>
-      <c r="AA31">
+      <c r="AA31" s="1">
         <v>0.00064291230122710645</v>
       </c>
-      <c r="AB31">
+      <c r="AB31" s="1">
         <v>-8.5872892437626424e-05</v>
       </c>
-      <c r="AC31">
+      <c r="AC31" s="1">
         <v>-0.00020080040443599189</v>
       </c>
-      <c r="AD31">
+      <c r="AD31" s="1">
         <v>-0.0001675484293951542</v>
       </c>
-      <c r="AE31">
+      <c r="AE31" s="1">
         <v>0.0023397168933973183</v>
       </c>
-      <c r="AF31">
+      <c r="AF31" s="1">
         <v>0.0058511660004065746</v>
       </c>
-      <c r="AG31">
+      <c r="AG31" s="1">
         <v>0.0023422985185736446</v>
       </c>
-      <c r="AH31">
+      <c r="AH31" s="1">
         <v>0.0023765463588318954</v>
       </c>
-      <c r="AI31">
+      <c r="AI31" s="1">
         <v>-0.00010230473694138304</v>
       </c>
-      <c r="AJ31">
+      <c r="AJ31" s="1">
         <v>-0.00059763040040209877</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>47</v>
-      </c>
-      <c r="B32">
+        <v>59</v>
+      </c>
+      <c r="B32" s="1">
         <v>-0.028208762282950089</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="1">
         <v>4.0964857850996425e-06</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="1">
         <v>1.3543846875278972e-05</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="1">
         <v>-1.7557529951821934e-07</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="1">
         <v>7.8154354526771205e-05</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="1">
         <v>-0.00020877533717341399</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
         <v>-0.00010126996629608045</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="1">
         <v>-5.136319816392463e-05</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="1">
         <v>-5.7114362777859906e-05</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="1">
         <v>1.8751441248913286e-05</v>
       </c>
-      <c r="L32">
+      <c r="L32" s="1">
         <v>1.113046996905053e-06</v>
       </c>
-      <c r="M32">
+      <c r="M32" s="1">
         <v>-2.6975695680765777e-06</v>
       </c>
-      <c r="N32">
+      <c r="N32" s="1">
         <v>0.00015228951832689519</v>
       </c>
-      <c r="O32">
+      <c r="O32" s="1">
         <v>5.0847314204464336e-07</v>
       </c>
-      <c r="P32">
+      <c r="P32" s="1">
         <v>0.0010502261299347726</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" s="1">
         <v>0.0011976764371556259</v>
       </c>
-      <c r="R32">
+      <c r="R32" s="1">
         <v>0.0012324113330018927</v>
       </c>
-      <c r="S32">
+      <c r="S32" s="1">
         <v>0.0012494126615120171</v>
       </c>
-      <c r="T32">
+      <c r="T32" s="1">
         <v>-9.5243304870931515e-05</v>
       </c>
-      <c r="U32">
+      <c r="U32" s="1">
         <v>5.1080740723754691e-05</v>
       </c>
-      <c r="V32">
+      <c r="V32" s="1">
         <v>0.0010070784718125836</v>
       </c>
-      <c r="W32">
+      <c r="W32" s="1">
         <v>0.001063323350324441</v>
       </c>
-      <c r="X32">
+      <c r="X32" s="1">
         <v>0.0010840283227032677</v>
       </c>
-      <c r="Y32">
+      <c r="Y32" s="1">
         <v>3.9922894881645743e-05</v>
       </c>
-      <c r="Z32">
+      <c r="Z32" s="1">
         <v>0.00026213878349254718</v>
       </c>
-      <c r="AA32">
+      <c r="AA32" s="1">
         <v>0.00043240917989592967</v>
       </c>
-      <c r="AB32">
+      <c r="AB32" s="1">
         <v>-2.2295642024893403e-05</v>
       </c>
-      <c r="AC32">
+      <c r="AC32" s="1">
         <v>-0.00021169311677380698</v>
       </c>
-      <c r="AD32">
+      <c r="AD32" s="1">
         <v>4.5906587038217588e-05</v>
       </c>
-      <c r="AE32">
+      <c r="AE32" s="1">
         <v>0.002346704344400135</v>
       </c>
-      <c r="AF32">
+      <c r="AF32" s="1">
         <v>0.0023422985185736446</v>
       </c>
-      <c r="AG32">
+      <c r="AG32" s="1">
         <v>0.0043670630985107317</v>
       </c>
-      <c r="AH32">
+      <c r="AH32" s="1">
         <v>0.0023605833278101634</v>
       </c>
-      <c r="AI32">
+      <c r="AI32" s="1">
         <v>-8.9809236113880164e-05</v>
       </c>
-      <c r="AJ32">
+      <c r="AJ32" s="1">
         <v>-0.002130315052548713</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33">
+        <v>60</v>
+      </c>
+      <c r="B33" s="1">
         <v>-0.010719269184777256</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="1">
         <v>2.6431532404241927e-05</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="1">
         <v>2.3196172085687456e-05</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="1">
         <v>-2.8066445402455033e-07</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="1">
         <v>4.9433677127690492e-05</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="1">
         <v>-7.454045390739236e-05</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="1">
         <v>-3.0030860401207321e-05</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="1">
         <v>-8.6017566017499228e-05</v>
       </c>
-      <c r="J33">
+      <c r="J33" s="1">
         <v>-2.0336837245263661e-05</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="1">
         <v>-3.0605399630216461e-05</v>
       </c>
-      <c r="L33">
+      <c r="L33" s="1">
         <v>1.0164044238391507e-05</v>
       </c>
-      <c r="M33">
+      <c r="M33" s="1">
         <v>2.2541244670759591e-05</v>
       </c>
-      <c r="N33">
+      <c r="N33" s="1">
         <v>0.00016018630743554717</v>
       </c>
-      <c r="O33">
+      <c r="O33" s="1">
         <v>2.8606393510425773e-07</v>
       </c>
-      <c r="P33">
+      <c r="P33" s="1">
         <v>0.00053820313139241183</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" s="1">
         <v>-9.468572262855135e-05</v>
       </c>
-      <c r="R33">
+      <c r="R33" s="1">
         <v>0.00043938872795945549</v>
       </c>
-      <c r="S33">
+      <c r="S33" s="1">
         <v>0.00030299708893311017</v>
       </c>
-      <c r="T33">
+      <c r="T33" s="1">
         <v>-3.8673588672727128e-06</v>
       </c>
-      <c r="U33">
+      <c r="U33" s="1">
         <v>-8.7232181652158397e-05</v>
       </c>
-      <c r="V33">
+      <c r="V33" s="1">
         <v>0.00030001005084773213</v>
       </c>
-      <c r="W33">
+      <c r="W33" s="1">
         <v>0.00039969706077941369</v>
       </c>
-      <c r="X33">
+      <c r="X33" s="1">
         <v>0.0003755324623292422</v>
       </c>
-      <c r="Y33">
+      <c r="Y33" s="1">
         <v>-0.00020530490894841644</v>
       </c>
-      <c r="Z33">
+      <c r="Z33" s="1">
         <v>2.3607548957658986e-05</v>
       </c>
-      <c r="AA33">
+      <c r="AA33" s="1">
         <v>0.00010952341722379917</v>
       </c>
-      <c r="AB33">
+      <c r="AB33" s="1">
         <v>1.8459878584561841e-05</v>
       </c>
-      <c r="AC33">
+      <c r="AC33" s="1">
         <v>-9.2808848901034099e-05</v>
       </c>
-      <c r="AD33">
+      <c r="AD33" s="1">
         <v>-0.00029558782944295696</v>
       </c>
-      <c r="AE33">
+      <c r="AE33" s="1">
         <v>0.0023553422044259608</v>
       </c>
-      <c r="AF33">
+      <c r="AF33" s="1">
         <v>0.0023765463588318954</v>
       </c>
-      <c r="AG33">
+      <c r="AG33" s="1">
         <v>0.0023605833278101634</v>
       </c>
-      <c r="AH33">
+      <c r="AH33" s="1">
         <v>0.0033654598896860001</v>
       </c>
-      <c r="AI33">
+      <c r="AI33" s="1">
         <v>-9.2226319405075679e-05</v>
       </c>
-      <c r="AJ33">
+      <c r="AJ33" s="1">
         <v>-0.0014547838918821925</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>49</v>
-      </c>
-      <c r="B34">
+        <v>61</v>
+      </c>
+      <c r="B34" s="1">
         <v>-0.032685291730632712</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="1">
         <v>-1.6121058903087462e-06</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="1">
         <v>-2.3439814574275982e-06</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="1">
         <v>1.9860538207604083e-08</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="1">
         <v>2.8278999714072446e-05</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="1">
         <v>2.8253198276150871e-05</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="1">
         <v>9.0338800025934526e-06</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="1">
         <v>-3.9977422719899354e-06</v>
       </c>
-      <c r="J34">
+      <c r="J34" s="1">
         <v>4.3145150942345822e-06</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="1">
         <v>-2.289211513618666e-05</v>
       </c>
-      <c r="L34">
+      <c r="L34" s="1">
         <v>1.9581124250593224e-06</v>
       </c>
-      <c r="M34">
+      <c r="M34" s="1">
         <v>-1.5489790493394847e-06</v>
       </c>
-      <c r="N34">
+      <c r="N34" s="1">
         <v>2.4524342602590338e-05</v>
       </c>
-      <c r="O34">
+      <c r="O34" s="1">
         <v>-2.0498787930709806e-07</v>
       </c>
-      <c r="P34">
+      <c r="P34" s="1">
         <v>-0.00011393515887328509</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" s="1">
         <v>-7.3055139630642807e-05</v>
       </c>
-      <c r="R34">
+      <c r="R34" s="1">
         <v>-2.4431924458487297e-05</v>
       </c>
-      <c r="S34">
+      <c r="S34" s="1">
         <v>-8.9176985475641901e-06</v>
       </c>
-      <c r="T34">
+      <c r="T34" s="1">
         <v>-4.3407197007044439e-06</v>
       </c>
-      <c r="U34">
+      <c r="U34" s="1">
         <v>3.3292910232073179e-06</v>
       </c>
-      <c r="V34">
+      <c r="V34" s="1">
         <v>-9.4805823445676118e-05</v>
       </c>
-      <c r="W34">
+      <c r="W34" s="1">
         <v>-0.00010860416903446524</v>
       </c>
-      <c r="X34">
+      <c r="X34" s="1">
         <v>-0.00012355707058292476</v>
       </c>
-      <c r="Y34">
+      <c r="Y34" s="1">
         <v>-0.00017755753447758465</v>
       </c>
-      <c r="Z34">
+      <c r="Z34" s="1">
         <v>-0.00016395808673495046</v>
       </c>
-      <c r="AA34">
+      <c r="AA34" s="1">
         <v>-0.00017726224461141974</v>
       </c>
-      <c r="AB34">
+      <c r="AB34" s="1">
         <v>9.7761127252276399e-06</v>
       </c>
-      <c r="AC34">
+      <c r="AC34" s="1">
         <v>6.4212969890078476e-06</v>
       </c>
-      <c r="AD34">
+      <c r="AD34" s="1">
         <v>3.7173032135186159e-05</v>
       </c>
-      <c r="AE34">
+      <c r="AE34" s="1">
         <v>-8.4817085995199498e-05</v>
       </c>
-      <c r="AF34">
+      <c r="AF34" s="1">
         <v>-0.00010230473694138304</v>
       </c>
-      <c r="AG34">
+      <c r="AG34" s="1">
         <v>-8.9809236113880164e-05</v>
       </c>
-      <c r="AH34">
+      <c r="AH34" s="1">
         <v>-9.2226319405075679e-05</v>
       </c>
-      <c r="AI34">
+      <c r="AI34" s="1">
         <v>3.9077050663881231e-05</v>
       </c>
-      <c r="AJ34">
+      <c r="AJ34" s="1">
         <v>-0.00023830450607081056</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>50</v>
-      </c>
-      <c r="B35">
+        <v>62</v>
+      </c>
+      <c r="B35" s="1">
         <v>-0.36457167021954273</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="1">
         <v>0.00092003743403877721</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="1">
         <v>-0.00090510970622816782</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="1">
         <v>8.7595031674691282e-06</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="1">
         <v>-0.021139098024173419</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="1">
         <v>-0.0034325115170165924</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="1">
         <v>-0.0030527299963288078</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="1">
         <v>-0.0015780156982079727</v>
       </c>
-      <c r="J35">
+      <c r="J35" s="1">
         <v>0.00043247072984436285</v>
       </c>
-      <c r="K35">
+      <c r="K35" s="1">
         <v>-0.013487811945752215</v>
       </c>
-      <c r="L35">
+      <c r="L35" s="1">
         <v>0.00023705757003686758</v>
       </c>
-      <c r="M35">
+      <c r="M35" s="1">
         <v>1.3874728153586675e-05</v>
       </c>
-      <c r="N35">
+      <c r="N35" s="1">
         <v>-0.01529211463927518</v>
       </c>
-      <c r="O35">
+      <c r="O35" s="1">
         <v>-0.00047432476289304792</v>
       </c>
-      <c r="P35">
+      <c r="P35" s="1">
         <v>-0.70866197560460176</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" s="1">
         <v>-0.74579518558071944</v>
       </c>
-      <c r="R35">
+      <c r="R35" s="1">
         <v>-0.75293696522668818</v>
       </c>
-      <c r="S35">
+      <c r="S35" s="1">
         <v>-0.75433967873682439</v>
       </c>
-      <c r="T35">
+      <c r="T35" s="1">
         <v>0.0020266660619707036</v>
       </c>
-      <c r="U35">
+      <c r="U35" s="1">
         <v>0.0092554569361103511</v>
       </c>
-      <c r="V35">
+      <c r="V35" s="1">
         <v>-0.95596920904121663</v>
       </c>
-      <c r="W35">
+      <c r="W35" s="1">
         <v>-0.95602778939077449</v>
       </c>
-      <c r="X35">
+      <c r="X35" s="1">
         <v>-0.95256900919423559</v>
       </c>
-      <c r="Y35">
+      <c r="Y35" s="1">
         <v>-0.10931535525606169</v>
       </c>
-      <c r="Z35">
+      <c r="Z35" s="1">
         <v>-0.095520386018529649</v>
       </c>
-      <c r="AA35">
+      <c r="AA35" s="1">
         <v>-0.097042069255456928</v>
       </c>
-      <c r="AB35">
+      <c r="AB35" s="1">
         <v>-0.0032743294009943587</v>
       </c>
-      <c r="AC35">
+      <c r="AC35" s="1">
         <v>-0.0021239170953026316</v>
       </c>
-      <c r="AD35">
+      <c r="AD35" s="1">
         <v>-0.012471229429938935</v>
       </c>
-      <c r="AE35">
+      <c r="AE35" s="1">
         <v>-0.0031902200192739576</v>
       </c>
-      <c r="AF35">
+      <c r="AF35" s="1">
         <v>-0.00059763040040209877</v>
       </c>
-      <c r="AG35">
+      <c r="AG35" s="1">
         <v>-0.002130315052548713</v>
       </c>
-      <c r="AH35">
+      <c r="AH35" s="1">
         <v>-0.0014547838918821925</v>
       </c>
-      <c r="AI35">
+      <c r="AI35" s="1">
         <v>-0.00023830450607081056</v>
       </c>
-      <c r="AJ35">
+      <c r="AJ35" s="1">
         <v>1.0813984114360218</v>
       </c>
     </row>
@@ -4426,2859 +4429,2856 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AF30"/>
+  <dimension ref="A1:AE30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="G1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="H1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" t="s">
+        <v>66</v>
+      </c>
+      <c r="N1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" t="s">
+        <v>67</v>
+      </c>
+      <c r="P1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S1" t="s">
+        <v>50</v>
+      </c>
+      <c r="T1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V1" t="s">
+        <v>53</v>
+      </c>
+      <c r="W1" t="s">
+        <v>54</v>
+      </c>
+      <c r="X1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z1" t="s">
         <v>57</v>
       </c>
-      <c r="J1" t="s">
+      <c r="AA1" t="s">
         <v>58</v>
       </c>
-      <c r="K1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="AB1" t="s">
         <v>59</v>
       </c>
-      <c r="N1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="AC1" t="s">
         <v>60</v>
       </c>
-      <c r="P1" t="s">
+      <c r="AD1" t="s">
         <v>61</v>
       </c>
-      <c r="Q1" t="s">
-        <v>36</v>
-      </c>
-      <c r="R1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S1" t="s">
-        <v>38</v>
-      </c>
-      <c r="T1" t="s">
-        <v>39</v>
-      </c>
-      <c r="U1" t="s">
-        <v>40</v>
-      </c>
-      <c r="V1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X1" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>49</v>
-      </c>
       <c r="AE1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2">
+        <v>29</v>
+      </c>
+      <c r="B2" s="1">
         <v>-0.026065445684737822</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>0.0010329465613448088</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>1.4262351818613486e-05</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>-1.5220740977833763e-07</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>0.00049279310043409349</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>0.00057092305716710296</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>0.00045928095657984719</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <v>0.00042904435988835019</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <v>3.1139249018332364e-05</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>-6.7169592573585287e-05</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <v>-2.3114111765889159e-05</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <v>-1.090563120819644e-05</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="1">
         <v>-0.0010165483732742387</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="1">
         <v>-2.654712436017221e-05</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="1">
         <v>2.2352358193830505e-05</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="1">
         <v>-0.00044570274371215715</v>
       </c>
-      <c r="R2">
+      <c r="R2" s="1">
         <v>-0.00040354915424791783</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="1">
         <v>-0.0002314781141994317</v>
       </c>
-      <c r="T2">
+      <c r="T2" s="1">
         <v>-0.00041282656615511523</v>
       </c>
-      <c r="U2">
+      <c r="U2" s="1">
         <v>-0.00035026378957126234</v>
       </c>
-      <c r="V2">
+      <c r="V2" s="1">
         <v>-0.00021178024689734142</v>
       </c>
-      <c r="W2">
+      <c r="W2" s="1">
         <v>0.00012750548868191601</v>
       </c>
-      <c r="X2">
+      <c r="X2" s="1">
         <v>0.00024006778430824433</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" s="1">
         <v>0.00057460869055593687</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" s="1">
         <v>-5.9639220337907624e-05</v>
       </c>
-      <c r="AA2">
+      <c r="AA2" s="1">
         <v>-7.9219937628110788e-05</v>
       </c>
-      <c r="AB2">
+      <c r="AB2" s="1">
         <v>3.8405483266120571e-05</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" s="1">
         <v>-8.478422187331713e-05</v>
       </c>
-      <c r="AD2">
+      <c r="AD2" s="1">
         <v>7.6191141681226573e-06</v>
       </c>
-      <c r="AE2">
+      <c r="AE2" s="1">
         <v>-0.00066283310454956111</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3">
+        <v>30</v>
+      </c>
+      <c r="B3" s="1">
         <v>-0.0079172851678788563</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>1.4262351818613486e-05</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>4.6215607629481497e-05</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>-4.8015047199015958e-07</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>0.00017540076532389652</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>0.00016365783011594646</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>0.00017505671082507787</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>0.00021251719922700638</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>-2.1377274110581288e-06</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>-1.8049146115540636e-05</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <v>-4.2170923218194521e-06</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <v>-6.9136550191088242e-06</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="1">
         <v>-2.4456675121388736e-05</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="1">
         <v>5.8437571275367774e-06</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="1">
         <v>8.8778020334374561e-06</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="1">
         <v>3.2626414767878255e-05</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="1">
         <v>1.6230703902857767e-05</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="1">
         <v>4.7002925702909057e-05</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="1">
         <v>1.0880688030440351e-05</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="1">
         <v>-0.00010855265839014106</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="1">
         <v>3.9597010241052086e-05</v>
       </c>
-      <c r="W3">
+      <c r="W3" s="1">
         <v>1.7347547974843963e-05</v>
       </c>
-      <c r="X3">
+      <c r="X3" s="1">
         <v>0.00010356571509978526</v>
       </c>
-      <c r="Y3">
+      <c r="Y3" s="1">
         <v>2.002318225931938e-05</v>
       </c>
-      <c r="Z3">
+      <c r="Z3" s="1">
         <v>-3.1789624952075824e-05</v>
       </c>
-      <c r="AA3">
+      <c r="AA3" s="1">
         <v>-7.5855901729021799e-05</v>
       </c>
-      <c r="AB3">
+      <c r="AB3" s="1">
         <v>-2.1657878400881234e-05</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="1">
         <v>-3.3353497673813148e-05</v>
       </c>
-      <c r="AD3">
+      <c r="AD3" s="1">
         <v>-1.1085362276545344e-06</v>
       </c>
-      <c r="AE3">
+      <c r="AE3" s="1">
         <v>-0.0010483699560981065</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4">
+        <v>31</v>
+      </c>
+      <c r="B4" s="1">
         <v>7.3230376897144179e-05</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>-1.5220740977833763e-07</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>-4.8015047199015958e-07</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>5.2221706464782142e-09</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>-2.0411165090727172e-06</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>-1.7865569073606485e-06</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>-1.7848432523730681e-06</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>-2.1026049470883805e-06</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>2.7313027284348609e-08</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>1.6398772990690155e-07</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <v>3.0752684694149591e-08</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <v>7.0150814517455251e-08</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="1">
         <v>2.3513460583800457e-07</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>-3.0301502254415553e-08</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="1">
         <v>-1.3155641162606376e-07</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="1">
         <v>-4.8621227783461805e-07</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="1">
         <v>-2.5345450365754152e-07</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <v>-5.7379765961421535e-07</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="1">
         <v>-7.1393451806931791e-08</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="1">
         <v>9.2298827362352935e-07</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="1">
         <v>-1.1339498653628081e-06</v>
       </c>
-      <c r="W4">
+      <c r="W4" s="1">
         <v>1.2791066168793867e-07</v>
       </c>
-      <c r="X4">
+      <c r="X4" s="1">
         <v>-9.1130124346423506e-07</v>
       </c>
-      <c r="Y4">
+      <c r="Y4" s="1">
         <v>5.4440074041411606e-08</v>
       </c>
-      <c r="Z4">
+      <c r="Z4" s="1">
         <v>2.9470200298713153e-07</v>
       </c>
-      <c r="AA4">
+      <c r="AA4" s="1">
         <v>6.6148130999926827e-07</v>
       </c>
-      <c r="AB4">
+      <c r="AB4" s="1">
         <v>1.2153867929663458e-07</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="1">
         <v>3.3168461507984337e-07</v>
       </c>
-      <c r="AD4">
+      <c r="AD4" s="1">
         <v>8.2156557945128462e-09</v>
       </c>
-      <c r="AE4">
+      <c r="AE4" s="1">
         <v>1.0640581856787739e-05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5">
+        <v>33</v>
+      </c>
+      <c r="B5" s="1">
         <v>0.37281829748337419</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>0.00049279310043409349</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>0.00017540076532389652</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>-2.0411165090727172e-06</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>0.031389993568030315</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>0.029655579773306698</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>0.029532929101101918</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <v>0.029618977565565641</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <v>-5.7277390843675675e-05</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>-8.2269009300922277e-05</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <v>-1.81403150521424e-05</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <v>-0.00017703657817094536</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="1">
         <v>-0.00045206432634114276</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>6.704304238346016e-05</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="1">
         <v>0.00018113520440454171</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="1">
         <v>-3.0781087584155764e-05</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="1">
         <v>0.00060241158390449481</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>0.00077933488211934243</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="1">
         <v>0.00023143792741475017</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="1">
         <v>-1.1329617287378357e-05</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="1">
         <v>0.00072391870623428334</v>
       </c>
-      <c r="W5">
+      <c r="W5" s="1">
         <v>-0.00055532591218849028</v>
       </c>
-      <c r="X5">
+      <c r="X5" s="1">
         <v>-0.00048248197225675123</v>
       </c>
-      <c r="Y5">
+      <c r="Y5" s="1">
         <v>-4.7278258235658108e-05</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="1">
         <v>-8.274622861315431e-06</v>
       </c>
-      <c r="AA5">
+      <c r="AA5" s="1">
         <v>3.6117368855440556e-05</v>
       </c>
-      <c r="AB5">
+      <c r="AB5" s="1">
         <v>9.2353546964304457e-05</v>
       </c>
-      <c r="AC5">
+      <c r="AC5" s="1">
         <v>-0.00057841159540590603</v>
       </c>
-      <c r="AD5">
+      <c r="AD5" s="1">
         <v>9.0671573065469928e-06</v>
       </c>
-      <c r="AE5">
+      <c r="AE5" s="1">
         <v>-0.032159784235063139</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6">
+        <v>34</v>
+      </c>
+      <c r="B6" s="1">
         <v>0.28806600101490459</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>0.00057092305716710296</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>0.00016365783011594646</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>-1.7865569073606485e-06</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>0.029655579773306698</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>0.03007196512321611</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>0.029473148458009388</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <v>0.029567266604209726</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <v>6.1681316383629427e-05</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>-5.0386652137629842e-05</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <v>-5.7304292992973517e-05</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <v>-0.00022565357115437567</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="1">
         <v>-0.00050904627070896434</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="1">
         <v>-0.00021593840785975784</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="1">
         <v>0.00042748956346698973</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="1">
         <v>-0.00010962057610293049</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="1">
         <v>0.00044952374145083504</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="1">
         <v>0.00062796073051347989</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="1">
         <v>0.00022985671717497963</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="1">
         <v>0.00025924358028509703</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="1">
         <v>0.0004683967695791047</v>
       </c>
-      <c r="W6">
+      <c r="W6" s="1">
         <v>-0.00042263015504917598</v>
       </c>
-      <c r="X6">
+      <c r="X6" s="1">
         <v>-0.00020961733004112545</v>
       </c>
-      <c r="Y6">
+      <c r="Y6" s="1">
         <v>8.3951859641511264e-05</v>
       </c>
-      <c r="Z6">
+      <c r="Z6" s="1">
         <v>-3.9261213249722204e-06</v>
       </c>
-      <c r="AA6">
+      <c r="AA6" s="1">
         <v>0.00018734315537094308</v>
       </c>
-      <c r="AB6">
+      <c r="AB6" s="1">
         <v>8.1329546932472178e-05</v>
       </c>
-      <c r="AC6">
+      <c r="AC6" s="1">
         <v>-0.0005052037303517453</v>
       </c>
-      <c r="AD6">
+      <c r="AD6" s="1">
         <v>-1.2349192065575182e-06</v>
       </c>
-      <c r="AE6">
+      <c r="AE6" s="1">
         <v>-0.032280126940576095</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7">
+        <v>35</v>
+      </c>
+      <c r="B7" s="1">
         <v>0.23933577618724269</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>0.00045928095657984719</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>0.00017505671082507787</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>-1.7848432523730681e-06</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>0.029532929101101918</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>0.029473148458009388</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>0.029946457546608421</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="1">
         <v>0.029790096134696194</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>4.7132597792663537e-05</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>-8.3157106069845985e-05</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>-7.5685384915900617e-05</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>-0.00017500413676925248</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>-0.00047180129364613474</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>5.7116878483187521e-05</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="1">
         <v>6.4755587807915731e-05</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="1">
         <v>-0.00027770510114833585</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="1">
         <v>0.00021972232276121217</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="1">
         <v>0.00034674360831216805</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="1">
         <v>5.7687717225758661e-05</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="1">
         <v>-6.5326640725109353e-05</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="1">
         <v>8.7922992040259662e-05</v>
       </c>
-      <c r="W7">
+      <c r="W7" s="1">
         <v>-0.00032585619519723882</v>
       </c>
-      <c r="X7">
+      <c r="X7" s="1">
         <v>-0.00022134929284794774</v>
       </c>
-      <c r="Y7">
+      <c r="Y7" s="1">
         <v>-3.1540853646823408e-06</v>
       </c>
-      <c r="Z7">
+      <c r="Z7" s="1">
         <v>1.4577928968700568e-05</v>
       </c>
-      <c r="AA7">
+      <c r="AA7" s="1">
         <v>-7.8539598587877048e-05</v>
       </c>
-      <c r="AB7">
+      <c r="AB7" s="1">
         <v>7.5939079062429041e-05</v>
       </c>
-      <c r="AC7">
+      <c r="AC7" s="1">
         <v>-0.00043920405845935574</v>
       </c>
-      <c r="AD7">
+      <c r="AD7" s="1">
         <v>-2.129269578395542e-06</v>
       </c>
-      <c r="AE7">
+      <c r="AE7" s="1">
         <v>-0.032381623799499062</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8">
+        <v>64</v>
+      </c>
+      <c r="B8" s="1">
         <v>0.15162924209448761</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>0.00042904435988835019</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>0.00021251719922700638</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>-2.1026049470883805e-06</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>0.029618977565565641</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>0.029567266604209726</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>0.029790096134696194</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="1">
         <v>0.031354564877978719</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="1">
         <v>0.00029373767825653565</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>-0.00017294290828725589</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="1">
         <v>-8.823710751640755e-05</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="1">
         <v>-0.00038714107042592781</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="1">
         <v>-0.00050407904097357192</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="1">
         <v>-7.4047205353023476e-05</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="1">
         <v>8.8908063432213864e-05</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="1">
         <v>-0.00027562459175084486</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="1">
         <v>6.6608533423811317e-05</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="1">
         <v>6.2980907000707853e-05</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="1">
         <v>-0.00052414148897631657</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="1">
         <v>-0.00073477406976357046</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="1">
         <v>-0.00051367387239800721</v>
       </c>
-      <c r="W8">
+      <c r="W8" s="1">
         <v>-0.00021717130117562128</v>
       </c>
-      <c r="X8">
+      <c r="X8" s="1">
         <v>-0.00020213301139880764</v>
       </c>
-      <c r="Y8">
+      <c r="Y8" s="1">
         <v>3.7312790054182948e-05</v>
       </c>
-      <c r="Z8">
+      <c r="Z8" s="1">
         <v>-0.00020288103260348959</v>
       </c>
-      <c r="AA8">
+      <c r="AA8" s="1">
         <v>-0.0001955523544125105</v>
       </c>
-      <c r="AB8">
+      <c r="AB8" s="1">
         <v>6.0704646345669661e-05</v>
       </c>
-      <c r="AC8">
+      <c r="AC8" s="1">
         <v>-0.00061212124498428826</v>
       </c>
-      <c r="AD8">
+      <c r="AD8" s="1">
         <v>1.5926877012795702e-05</v>
       </c>
-      <c r="AE8">
+      <c r="AE8" s="1">
         <v>-0.033017364064007113</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9">
+        <v>65</v>
+      </c>
+      <c r="B9" s="1">
         <v>0.529636959522233</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>3.1139249018332364e-05</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>-2.1377274110581288e-06</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="1">
         <v>2.7313027284348609e-08</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>-5.7277390843675675e-05</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>6.1681316383629427e-05</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>4.7132597792663537e-05</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>0.00029373767825653565</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="1">
         <v>0.00069768878039776542</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>-3.8256548465860559e-05</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="1">
         <v>-7.5763755379625882e-06</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="1">
         <v>-0.00055256563670820285</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="1">
         <v>-4.2407139895438166e-05</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="1">
         <v>-0.00067674335476308365</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="1">
         <v>0.00051120737268737148</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="1">
         <v>-0.00069996964843220934</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="1">
         <v>-0.00064891309294484636</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="1">
         <v>-0.00073328027613313383</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="1">
         <v>-0.00043840825848071507</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="1">
         <v>-0.00024584765560516325</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="1">
         <v>-0.00022653945311208246</v>
       </c>
-      <c r="W9">
+      <c r="W9" s="1">
         <v>-0.00014065289554036241</v>
       </c>
-      <c r="X9">
+      <c r="X9" s="1">
         <v>-0.000137000195912826</v>
       </c>
-      <c r="Y9">
+      <c r="Y9" s="1">
         <v>-0.00010271707597833408</v>
       </c>
-      <c r="Z9">
+      <c r="Z9" s="1">
         <v>-7.3754935865742472e-05</v>
       </c>
-      <c r="AA9">
+      <c r="AA9" s="1">
         <v>0.00026633145562040704</v>
       </c>
-      <c r="AB9">
+      <c r="AB9" s="1">
         <v>7.3325307039152248e-06</v>
       </c>
-      <c r="AC9">
+      <c r="AC9" s="1">
         <v>-5.2816937804775965e-05</v>
       </c>
-      <c r="AD9">
+      <c r="AD9" s="1">
         <v>-5.7424220582816448e-07</v>
       </c>
-      <c r="AE9">
+      <c r="AE9" s="1">
         <v>0.00054327732350461925</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10">
+        <v>37</v>
+      </c>
+      <c r="B10" s="1">
         <v>0.044694689529177475</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>-6.7169592573585287e-05</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>-1.8049146115540636e-05</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>1.6398772990690155e-07</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>-8.2269009300922277e-05</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>-5.0386652137629842e-05</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>-8.3157106069845985e-05</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="1">
         <v>-0.00017294290828725589</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
         <v>-3.8256548465860559e-05</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0.0007340363823226954</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="1">
         <v>-4.4150594259680834e-05</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="1">
         <v>-9.2479770423388192e-05</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="1">
         <v>6.2521272164796186e-05</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="1">
         <v>1.490929010443333e-05</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="1">
         <v>0.00010918583230875916</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="1">
         <v>0.00046894769478696054</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>0.00052830617987288143</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="1">
         <v>0.00043458881287782806</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="1">
         <v>0.0047493075428773884</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="1">
         <v>0.0048086785295841702</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="1">
         <v>0.0047456891429918276</v>
       </c>
-      <c r="W10">
+      <c r="W10" s="1">
         <v>-0.00017679758522371738</v>
       </c>
-      <c r="X10">
+      <c r="X10" s="1">
         <v>-2.4026820681088154e-05</v>
       </c>
-      <c r="Y10">
+      <c r="Y10" s="1">
         <v>-9.2081775341186153e-06</v>
       </c>
-      <c r="Z10">
+      <c r="Z10" s="1">
         <v>-7.6069061098844523e-05</v>
       </c>
-      <c r="AA10">
+      <c r="AA10" s="1">
         <v>0.00018760173511020981</v>
       </c>
-      <c r="AB10">
+      <c r="AB10" s="1">
         <v>-1.7714324571826935e-05</v>
       </c>
-      <c r="AC10">
+      <c r="AC10" s="1">
         <v>2.938214195455412e-05</v>
       </c>
-      <c r="AD10">
+      <c r="AD10" s="1">
         <v>8.4350494529750772e-07</v>
       </c>
-      <c r="AE10">
+      <c r="AE10" s="1">
         <v>-0.0042891616651933974</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11">
+        <v>38</v>
+      </c>
+      <c r="B11" s="1">
         <v>-0.00028349834435072765</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>-2.3114111765889159e-05</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>-4.2170923218194521e-06</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>3.0752684694149591e-08</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>-1.81403150521424e-05</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>-5.7304292992973517e-05</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>-7.5685384915900617e-05</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="1">
         <v>-8.823710751640755e-05</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="1">
         <v>-7.5763755379625882e-06</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>-4.4150594259680834e-05</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="1">
         <v>5.353111976214432e-05</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="1">
         <v>1.0792251322212581e-05</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="1">
         <v>2.6194447701374644e-05</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="1">
         <v>5.2016103126589446e-06</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="1">
         <v>-7.4847593122385851e-06</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="1">
         <v>2.8397319384575203e-06</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="1">
         <v>-1.6315875199062618e-05</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="1">
         <v>-2.5928667252522318e-05</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="1">
         <v>-3.0200514097221474e-05</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="1">
         <v>-9.517160253641097e-06</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="1">
         <v>1.1527451008573695e-05</v>
       </c>
-      <c r="W11">
+      <c r="W11" s="1">
         <v>-3.1861570127550163e-05</v>
       </c>
-      <c r="X11">
+      <c r="X11" s="1">
         <v>-8.834922092340719e-06</v>
       </c>
-      <c r="Y11">
+      <c r="Y11" s="1">
         <v>-7.001061118564951e-05</v>
       </c>
-      <c r="Z11">
+      <c r="Z11" s="1">
         <v>-3.5337271989710787e-06</v>
       </c>
-      <c r="AA11">
+      <c r="AA11" s="1">
         <v>-2.7597800246015965e-06</v>
       </c>
-      <c r="AB11">
+      <c r="AB11" s="1">
         <v>4.0818113271684974e-06</v>
       </c>
-      <c r="AC11">
+      <c r="AC11" s="1">
         <v>-4.7167480330407695e-06</v>
       </c>
-      <c r="AD11">
+      <c r="AD11" s="1">
         <v>-7.2616839099441904e-07</v>
       </c>
-      <c r="AE11">
+      <c r="AE11" s="1">
         <v>0.00020675770649089548</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12">
+        <v>66</v>
+      </c>
+      <c r="B12" s="1">
         <v>0.18901751161164429</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>-1.090563120819644e-05</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
         <v>-6.9136550191088242e-06</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="1">
         <v>7.0150814517455251e-08</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>-0.00017703657817094536</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>-0.00022565357115437567</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>-0.00017500413676925248</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="1">
         <v>-0.00038714107042592781</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="1">
         <v>-0.00055256563670820285</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>-9.2479770423388192e-05</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="1">
         <v>1.0792251322212581e-05</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="1">
         <v>0.00068995668392866905</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="1">
         <v>2.2806321996098884e-05</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="1">
         <v>0.00055228669010431238</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="1">
         <v>-0.00066880312201880797</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="1">
         <v>-0.00028835414344694865</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="1">
         <v>-0.00035469042608451479</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="1">
         <v>-0.00045929049616429064</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="1">
         <v>-0.00053533352260040743</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="1">
         <v>-0.00066937312766823711</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="1">
         <v>-0.00064260445259013157</v>
       </c>
-      <c r="W12">
+      <c r="W12" s="1">
         <v>0.00015215144773399658</v>
       </c>
-      <c r="X12">
+      <c r="X12" s="1">
         <v>8.778081315901128e-05</v>
       </c>
-      <c r="Y12">
+      <c r="Y12" s="1">
         <v>3.0950299204906423e-06</v>
       </c>
-      <c r="Z12">
+      <c r="Z12" s="1">
         <v>0.00013008005949504908</v>
       </c>
-      <c r="AA12">
+      <c r="AA12" s="1">
         <v>-0.0003100072054568739</v>
       </c>
-      <c r="AB12">
+      <c r="AB12" s="1">
         <v>-2.3793157072006491e-06</v>
       </c>
-      <c r="AC12">
+      <c r="AC12" s="1">
         <v>8.0303001155676297e-05</v>
       </c>
-      <c r="AD12">
+      <c r="AD12" s="1">
         <v>-8.97690709157089e-06</v>
       </c>
-      <c r="AE12">
+      <c r="AE12" s="1">
         <v>0.00088216900507231283</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13">
+        <v>40</v>
+      </c>
+      <c r="B13" s="1">
         <v>0.07512107694846791</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>-0.0010165483732742387</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>-2.4456675121388736e-05</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>2.3513460583800457e-07</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>-0.00045206432634114276</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>-0.00050904627070896434</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>-0.00047180129364613474</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="1">
         <v>-0.00050407904097357192</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="1">
         <v>-4.2407139895438166e-05</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>6.2521272164796186e-05</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="1">
         <v>2.6194447701374644e-05</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="1">
         <v>2.2806321996098884e-05</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="1">
         <v>0.0072088958857074161</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="1">
         <v>-0.0014753859630328755</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="1">
         <v>0.00038238735518371912</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="1">
         <v>-0.00093571041553573231</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="1">
         <v>-0.00094865199538002884</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="1">
         <v>-0.0011199044033452512</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="1">
         <v>0.00033631891289902065</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="1">
         <v>0.00034087941301499166</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="1">
         <v>0.00019892323421951026</v>
       </c>
-      <c r="W13">
+      <c r="W13" s="1">
         <v>-0.00013300244085214235</v>
       </c>
-      <c r="X13">
+      <c r="X13" s="1">
         <v>-0.00024683385865011148</v>
       </c>
-      <c r="Y13">
+      <c r="Y13" s="1">
         <v>-0.0005386836053062052</v>
       </c>
-      <c r="Z13">
+      <c r="Z13" s="1">
         <v>0.00036257974665770943</v>
       </c>
-      <c r="AA13">
+      <c r="AA13" s="1">
         <v>0.00035269722652658554</v>
       </c>
-      <c r="AB13">
+      <c r="AB13" s="1">
         <v>0.00032703229103266162</v>
       </c>
-      <c r="AC13">
+      <c r="AC13" s="1">
         <v>0.00030707311059573889</v>
       </c>
-      <c r="AD13">
+      <c r="AD13" s="1">
         <v>-1.4065500302039036e-05</v>
       </c>
-      <c r="AE13">
+      <c r="AE13" s="1">
         <v>0.0021511976125625494</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14">
+        <v>67</v>
+      </c>
+      <c r="B14" s="1">
         <v>0.13007630024440825</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>-2.654712436017221e-05</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>5.8437571275367774e-06</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>-3.0301502254415553e-08</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>6.704304238346016e-05</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>-0.00021593840785975784</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>5.7116878483187521e-05</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="1">
         <v>-7.4047205353023476e-05</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="1">
         <v>-0.00067674335476308365</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>1.490929010443333e-05</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="1">
         <v>5.2016103126589446e-06</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="1">
         <v>0.00055228669010431238</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="1">
         <v>-0.0014753859630328755</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="1">
         <v>0.015703381821079741</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="1">
         <v>-0.014338068806649243</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="1">
         <v>0.0056349892330915669</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="1">
         <v>0.0055585670791436399</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="1">
         <v>0.0056179338391391734</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="1">
         <v>0.00024373630501534765</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="1">
         <v>8.2840118661754725e-05</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="1">
         <v>6.9427346273062684e-05</v>
       </c>
-      <c r="W14">
+      <c r="W14" s="1">
         <v>0.00018359187108268893</v>
       </c>
-      <c r="X14">
+      <c r="X14" s="1">
         <v>0.00013580242968350912</v>
       </c>
-      <c r="Y14">
+      <c r="Y14" s="1">
         <v>0.00011973015689055282</v>
       </c>
-      <c r="Z14">
+      <c r="Z14" s="1">
         <v>-0.00017477844842983536</v>
       </c>
-      <c r="AA14">
+      <c r="AA14" s="1">
         <v>-0.00060388969100810472</v>
       </c>
-      <c r="AB14">
+      <c r="AB14" s="1">
         <v>-0.00017826341878419538</v>
       </c>
-      <c r="AC14">
+      <c r="AC14" s="1">
         <v>-0.00017719232418892013</v>
       </c>
-      <c r="AD14">
+      <c r="AD14" s="1">
         <v>-8.2050199883564089e-06</v>
       </c>
-      <c r="AE14">
+      <c r="AE14" s="1">
         <v>-0.0052289910423943256</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15">
+        <v>68</v>
+      </c>
+      <c r="B15" s="1">
         <v>0.022819736221464364</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>2.2352358193830505e-05</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>8.8778020334374561e-06</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>-1.3155641162606376e-07</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>0.00018113520440454171</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>0.00042748956346698973</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>6.4755587807915731e-05</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="1">
         <v>8.8908063432213864e-05</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="1">
         <v>0.00051120737268737148</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>0.00010918583230875916</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="1">
         <v>-7.4847593122385851e-06</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="1">
         <v>-0.00066880312201880797</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="1">
         <v>0.00038238735518371912</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="1">
         <v>-0.014338068806649243</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="1">
         <v>0.014609639565077447</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="1">
         <v>-0.00015778396950633447</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="1">
         <v>-5.8767914641368003e-05</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="1">
         <v>0.00010652073460035508</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="1">
         <v>0.00080996362833808287</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="1">
         <v>0.00079596930393377734</v>
       </c>
-      <c r="V15">
+      <c r="V15" s="1">
         <v>0.00078900667214682721</v>
       </c>
-      <c r="W15">
+      <c r="W15" s="1">
         <v>-0.00017247102022206171</v>
       </c>
-      <c r="X15">
+      <c r="X15" s="1">
         <v>-5.7222217754036376e-05</v>
       </c>
-      <c r="Y15">
+      <c r="Y15" s="1">
         <v>-1.9510205894155168e-06</v>
       </c>
-      <c r="Z15">
+      <c r="Z15" s="1">
         <v>-1.1593263959014865e-05</v>
       </c>
-      <c r="AA15">
+      <c r="AA15" s="1">
         <v>0.00041861049792983422</v>
       </c>
-      <c r="AB15">
+      <c r="AB15" s="1">
         <v>2.2547775313796657e-05</v>
       </c>
-      <c r="AC15">
+      <c r="AC15" s="1">
         <v>-5.6548651036884574e-06</v>
       </c>
-      <c r="AD15">
+      <c r="AD15" s="1">
         <v>1.2146008325630148e-05</v>
       </c>
-      <c r="AE15">
+      <c r="AE15" s="1">
         <v>-0.00057478633349137642</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16">
+        <v>48</v>
+      </c>
+      <c r="B16" s="1">
         <v>0.39098545082068803</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>-0.00044570274371215715</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>3.2626414767878255e-05</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>-4.8621227783461805e-07</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>-3.0781087584155764e-05</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>-0.00010962057610293049</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>-0.00027770510114833585</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="1">
         <v>-0.00027562459175084486</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1">
         <v>-0.00069996964843220934</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>0.00046894769478696054</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="1">
         <v>2.8397319384575203e-06</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="1">
         <v>-0.00028835414344694865</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="1">
         <v>-0.00093571041553573231</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="1">
         <v>0.0056349892330915669</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="1">
         <v>-0.00015778396950633447</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="1">
         <v>0.027125774595283009</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="1">
         <v>0.025945179440514318</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="1">
         <v>0.026414312788358429</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="1">
         <v>0.0083160536003364371</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="1">
         <v>0.0031994422281892698</v>
       </c>
-      <c r="V16">
+      <c r="V16" s="1">
         <v>0.0030606455880593797</v>
       </c>
-      <c r="W16">
+      <c r="W16" s="1">
         <v>-0.00017459686153538378</v>
       </c>
-      <c r="X16">
+      <c r="X16" s="1">
         <v>0.00024036109397861799</v>
       </c>
-      <c r="Y16">
+      <c r="Y16" s="1">
         <v>-0.00012334006359578792</v>
       </c>
-      <c r="Z16">
+      <c r="Z16" s="1">
         <v>-0.00037479259634923268</v>
       </c>
-      <c r="AA16">
+      <c r="AA16" s="1">
         <v>-0.00061327024037592659</v>
       </c>
-      <c r="AB16">
+      <c r="AB16" s="1">
         <v>0.00029154219733662154</v>
       </c>
-      <c r="AC16">
+      <c r="AC16" s="1">
         <v>-0.00027625801803186911</v>
       </c>
-      <c r="AD16">
+      <c r="AD16" s="1">
         <v>6.2893109497402528e-05</v>
       </c>
-      <c r="AE16">
+      <c r="AE16" s="1">
         <v>-0.026705710144383613</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17">
+        <v>49</v>
+      </c>
+      <c r="B17" s="1">
         <v>0.47210959922669149</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>-0.00040354915424791783</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>1.6230703902857767e-05</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>-2.5345450365754152e-07</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <v>0.00060241158390449481</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>0.00044952374145083504</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>0.00021972232276121217</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="1">
         <v>6.6608533423811317e-05</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1">
         <v>-0.00064891309294484636</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>0.00052830617987288143</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="1">
         <v>-1.6315875199062618e-05</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="1">
         <v>-0.00035469042608451479</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="1">
         <v>-0.00094865199538002884</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="1">
         <v>0.0055585670791436399</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="1">
         <v>-5.8767914641368003e-05</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="1">
         <v>0.025945179440514318</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="1">
         <v>0.026404242554910098</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="1">
         <v>0.026701213541264479</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="1">
         <v>0.0088659978919775617</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="1">
         <v>0.0036704617803071937</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="1">
         <v>0.0034142458472649628</v>
       </c>
-      <c r="W17">
+      <c r="W17" s="1">
         <v>-0.00011357789080977676</v>
       </c>
-      <c r="X17">
+      <c r="X17" s="1">
         <v>0.00033955877437322982</v>
       </c>
-      <c r="Y17">
+      <c r="Y17" s="1">
         <v>2.5452738225816007e-05</v>
       </c>
-      <c r="Z17">
+      <c r="Z17" s="1">
         <v>-0.00022994546565366369</v>
       </c>
-      <c r="AA17">
+      <c r="AA17" s="1">
         <v>-0.00047457318888571853</v>
       </c>
-      <c r="AB17">
+      <c r="AB17" s="1">
         <v>0.00026546051185756883</v>
       </c>
-      <c r="AC17">
+      <c r="AC17" s="1">
         <v>-0.00025554743819388576</v>
       </c>
-      <c r="AD17">
+      <c r="AD17" s="1">
         <v>3.7520876562416924e-05</v>
       </c>
-      <c r="AE17">
+      <c r="AE17" s="1">
         <v>-0.027217721212380534</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18">
+        <v>50</v>
+      </c>
+      <c r="B18" s="1">
         <v>0.51679079242368209</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>-0.0002314781141994317</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
         <v>4.7002925702909057e-05</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="1">
         <v>-5.7379765961421535e-07</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <v>0.00077933488211934243</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>0.00062796073051347989</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>0.00034674360831216805</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="1">
         <v>6.2980907000707853e-05</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="1">
         <v>-0.00073328027613313383</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>0.00043458881287782806</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="1">
         <v>-2.5928667252522318e-05</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="1">
         <v>-0.00045929049616429064</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="1">
         <v>-0.0011199044033452512</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="1">
         <v>0.0056179338391391734</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="1">
         <v>0.00010652073460035508</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="1">
         <v>0.026414312788358429</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="1">
         <v>0.026701213541264479</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="1">
         <v>0.028395412428027206</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="1">
         <v>0.0083403444429068219</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="1">
         <v>0.0033118841115301334</v>
       </c>
-      <c r="V18">
+      <c r="V18" s="1">
         <v>0.0030267173309265483</v>
       </c>
-      <c r="W18">
+      <c r="W18" s="1">
         <v>-6.5256545739370009e-05</v>
       </c>
-      <c r="X18">
+      <c r="X18" s="1">
         <v>0.00046544359918203326</v>
       </c>
-      <c r="Y18">
+      <c r="Y18" s="1">
         <v>0.00019293200440824443</v>
       </c>
-      <c r="Z18">
+      <c r="Z18" s="1">
         <v>-0.00041692341647540931</v>
       </c>
-      <c r="AA18">
+      <c r="AA18" s="1">
         <v>-0.00066574719625615841</v>
       </c>
-      <c r="AB18">
+      <c r="AB18" s="1">
         <v>8.8498594066968583e-05</v>
       </c>
-      <c r="AC18">
+      <c r="AC18" s="1">
         <v>-0.00047840835065110499</v>
       </c>
-      <c r="AD18">
+      <c r="AD18" s="1">
         <v>2.6651566647904312e-05</v>
       </c>
-      <c r="AE18">
+      <c r="AE18" s="1">
         <v>-0.027175455384372896</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19">
+        <v>51</v>
+      </c>
+      <c r="B19" s="1">
         <v>0.26081800281374118</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>-0.00041282656615511523</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>1.0880688030440351e-05</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>-7.1393451806931791e-08</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <v>0.00023143792741475017</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>0.00022985671717497963</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>5.7687717225758661e-05</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>-0.00052414148897631657</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="1">
         <v>-0.00043840825848071507</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>0.0047493075428773884</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="1">
         <v>-3.0200514097221474e-05</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="1">
         <v>-0.00053533352260040743</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="1">
         <v>0.00033631891289902065</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="1">
         <v>0.00024373630501534765</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="1">
         <v>0.00080996362833808287</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="1">
         <v>0.0083160536003364371</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="1">
         <v>0.0088659978919775617</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="1">
         <v>0.0083403444429068219</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="1">
         <v>0.038450401063681389</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="1">
         <v>0.033254876792710886</v>
       </c>
-      <c r="V19">
+      <c r="V19" s="1">
         <v>0.032763924336382352</v>
       </c>
-      <c r="W19">
+      <c r="W19" s="1">
         <v>-0.00079906332041816339</v>
       </c>
-      <c r="X19">
+      <c r="X19" s="1">
         <v>-7.0229347763736422e-05</v>
       </c>
-      <c r="Y19">
+      <c r="Y19" s="1">
         <v>-1.3753813432569595e-05</v>
       </c>
-      <c r="Z19">
+      <c r="Z19" s="1">
         <v>-0.00056676069011191849</v>
       </c>
-      <c r="AA19">
+      <c r="AA19" s="1">
         <v>0.00071006351039425153</v>
       </c>
-      <c r="AB19">
+      <c r="AB19" s="1">
         <v>0.00015575156277867</v>
       </c>
-      <c r="AC19">
+      <c r="AC19" s="1">
         <v>1.7833010439959746e-05</v>
       </c>
-      <c r="AD19">
+      <c r="AD19" s="1">
         <v>1.7057913603004023e-05</v>
       </c>
-      <c r="AE19">
+      <c r="AE19" s="1">
         <v>-0.038900343883523689</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20">
+        <v>52</v>
+      </c>
+      <c r="B20" s="1">
         <v>0.29555872349429507</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>-0.00035026378957126234</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>-0.00010855265839014106</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>9.2298827362352935e-07</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <v>-1.1329617287378357e-05</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>0.00025924358028509703</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>-6.5326640725109353e-05</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="1">
         <v>-0.00073477406976357046</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="1">
         <v>-0.00024584765560516325</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>0.0048086785295841702</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="1">
         <v>-9.517160253641097e-06</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="1">
         <v>-0.00066937312766823711</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="1">
         <v>0.00034087941301499166</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="1">
         <v>8.2840118661754725e-05</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="1">
         <v>0.00079596930393377734</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="1">
         <v>0.0031994422281892698</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="1">
         <v>0.0036704617803071937</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="1">
         <v>0.0033118841115301334</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="1">
         <v>0.033254876792710886</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="1">
         <v>0.034254553835154244</v>
       </c>
-      <c r="V20">
+      <c r="V20" s="1">
         <v>0.033325860517803216</v>
       </c>
-      <c r="W20">
+      <c r="W20" s="1">
         <v>-0.0013752057904059204</v>
       </c>
-      <c r="X20">
+      <c r="X20" s="1">
         <v>-0.00016534066356713151</v>
       </c>
-      <c r="Y20">
+      <c r="Y20" s="1">
         <v>-0.0004001353239428164</v>
       </c>
-      <c r="Z20">
+      <c r="Z20" s="1">
         <v>-0.00052327868167851774</v>
       </c>
-      <c r="AA20">
+      <c r="AA20" s="1">
         <v>0.0012880476859547605</v>
       </c>
-      <c r="AB20">
+      <c r="AB20" s="1">
         <v>6.8721448960805051e-05</v>
       </c>
-      <c r="AC20">
+      <c r="AC20" s="1">
         <v>0.00017809833788614074</v>
       </c>
-      <c r="AD20">
+      <c r="AD20" s="1">
         <v>1.1252003639994563e-05</v>
       </c>
-      <c r="AE20">
+      <c r="AE20" s="1">
         <v>-0.030962458147002658</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21">
+        <v>53</v>
+      </c>
+      <c r="B21" s="1">
         <v>0.21248930614550574</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>-0.00021178024689734142</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>3.9597010241052086e-05</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>-1.1339498653628081e-06</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <v>0.00072391870623428334</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>0.0004683967695791047</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>8.7922992040259662e-05</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="1">
         <v>-0.00051367387239800721</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="1">
         <v>-0.00022653945311208246</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>0.0047456891429918276</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="1">
         <v>1.1527451008573695e-05</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="1">
         <v>-0.00064260445259013157</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="1">
         <v>0.00019892323421951026</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="1">
         <v>6.9427346273062684e-05</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="1">
         <v>0.00078900667214682721</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="1">
         <v>0.0030606455880593797</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="1">
         <v>0.0034142458472649628</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="1">
         <v>0.0030267173309265483</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="1">
         <v>0.032763924336382352</v>
       </c>
-      <c r="U21">
+      <c r="U21" s="1">
         <v>0.033325860517803216</v>
       </c>
-      <c r="V21">
+      <c r="V21" s="1">
         <v>0.036024484931398829</v>
       </c>
-      <c r="W21">
+      <c r="W21" s="1">
         <v>-0.0013754737846130918</v>
       </c>
-      <c r="X21">
+      <c r="X21" s="1">
         <v>1.6202803657947148e-05</v>
       </c>
-      <c r="Y21">
+      <c r="Y21" s="1">
         <v>-0.00028946290885026316</v>
       </c>
-      <c r="Z21">
+      <c r="Z21" s="1">
         <v>-0.00052767744482099324</v>
       </c>
-      <c r="AA21">
+      <c r="AA21" s="1">
         <v>0.0011323823639680011</v>
       </c>
-      <c r="AB21">
+      <c r="AB21" s="1">
         <v>2.4245789086180941e-05</v>
       </c>
-      <c r="AC21">
+      <c r="AC21" s="1">
         <v>0.00013751175020742384</v>
       </c>
-      <c r="AD21">
+      <c r="AD21" s="1">
         <v>-2.9773852312897208e-06</v>
       </c>
-      <c r="AE21">
+      <c r="AE21" s="1">
         <v>-0.032909501336933288</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22">
+        <v>54</v>
+      </c>
+      <c r="B22" s="1">
         <v>0.082719323560651856</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>0.00012750548868191601</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>1.7347547974843963e-05</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>1.2791066168793867e-07</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <v>-0.00055532591218849028</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>-0.00042263015504917598</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>-0.00032585619519723882</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="1">
         <v>-0.00021717130117562128</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="1">
         <v>-0.00014065289554036241</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>-0.00017679758522371738</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="1">
         <v>-3.1861570127550163e-05</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="1">
         <v>0.00015215144773399658</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="1">
         <v>-0.00013300244085214235</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="1">
         <v>0.00018359187108268893</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="1">
         <v>-0.00017247102022206171</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="1">
         <v>-0.00017459686153538378</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="1">
         <v>-0.00011357789080977676</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="1">
         <v>-6.5256545739370009e-05</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="1">
         <v>-0.00079906332041816339</v>
       </c>
-      <c r="U22">
+      <c r="U22" s="1">
         <v>-0.0013752057904059204</v>
       </c>
-      <c r="V22">
+      <c r="V22" s="1">
         <v>-0.0013754737846130918</v>
       </c>
-      <c r="W22">
+      <c r="W22" s="1">
         <v>0.0020418716388739522</v>
       </c>
-      <c r="X22">
+      <c r="X22" s="1">
         <v>0.0011019816285174323</v>
       </c>
-      <c r="Y22">
+      <c r="Y22" s="1">
         <v>0.0014819542776581354</v>
       </c>
-      <c r="Z22">
+      <c r="Z22" s="1">
         <v>-4.7405490455784964e-05</v>
       </c>
-      <c r="AA22">
+      <c r="AA22" s="1">
         <v>-0.00049549683331368498</v>
       </c>
-      <c r="AB22">
+      <c r="AB22" s="1">
         <v>-0.00022043506450546613</v>
       </c>
-      <c r="AC22">
+      <c r="AC22" s="1">
         <v>-0.00014339447218155886</v>
       </c>
-      <c r="AD22">
+      <c r="AD22" s="1">
         <v>-1.2328893807200166e-05</v>
       </c>
-      <c r="AE22">
+      <c r="AE22" s="1">
         <v>-0.00018776335799809745</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23">
+        <v>55</v>
+      </c>
+      <c r="B23" s="1">
         <v>0.090046368523395884</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="1">
         <v>0.00024006778430824433</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="1">
         <v>0.00010356571509978526</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="1">
         <v>-9.1130124346423506e-07</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="1">
         <v>-0.00048248197225675123</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <v>-0.00020961733004112545</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>-0.00022134929284794774</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="1">
         <v>-0.00020213301139880764</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="1">
         <v>-0.000137000195912826</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="1">
         <v>-2.4026820681088154e-05</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="1">
         <v>-8.834922092340719e-06</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="1">
         <v>8.778081315901128e-05</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="1">
         <v>-0.00024683385865011148</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="1">
         <v>0.00013580242968350912</v>
       </c>
-      <c r="P23">
+      <c r="P23" s="1">
         <v>-5.7222217754036376e-05</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="1">
         <v>0.00024036109397861799</v>
       </c>
-      <c r="R23">
+      <c r="R23" s="1">
         <v>0.00033955877437322982</v>
       </c>
-      <c r="S23">
+      <c r="S23" s="1">
         <v>0.00046544359918203326</v>
       </c>
-      <c r="T23">
+      <c r="T23" s="1">
         <v>-7.0229347763736422e-05</v>
       </c>
-      <c r="U23">
+      <c r="U23" s="1">
         <v>-0.00016534066356713151</v>
       </c>
-      <c r="V23">
+      <c r="V23" s="1">
         <v>1.6202803657947148e-05</v>
       </c>
-      <c r="W23">
+      <c r="W23" s="1">
         <v>0.0011019816285174323</v>
       </c>
-      <c r="X23">
+      <c r="X23" s="1">
         <v>0.0019093507084174434</v>
       </c>
-      <c r="Y23">
+      <c r="Y23" s="1">
         <v>0.0012003935401280973</v>
       </c>
-      <c r="Z23">
+      <c r="Z23" s="1">
         <v>4.4959418244021679e-05</v>
       </c>
-      <c r="AA23">
+      <c r="AA23" s="1">
         <v>-0.00021971728382072248</v>
       </c>
-      <c r="AB23">
+      <c r="AB23" s="1">
         <v>5.6727730063895095e-05</v>
       </c>
-      <c r="AC23">
+      <c r="AC23" s="1">
         <v>9.8662396590051393e-05</v>
       </c>
-      <c r="AD23">
+      <c r="AD23" s="1">
         <v>-1.2377498639513462e-05</v>
       </c>
-      <c r="AE23">
+      <c r="AE23" s="1">
         <v>-0.0033783884902997504</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24">
+        <v>56</v>
+      </c>
+      <c r="B24" s="1">
         <v>0.13394401328244776</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="1">
         <v>0.00057460869055593687</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="1">
         <v>2.002318225931938e-05</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>5.4440074041411606e-08</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="1">
         <v>-4.7278258235658108e-05</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="1">
         <v>8.3951859641511264e-05</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>-3.1540853646823408e-06</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="1">
         <v>3.7312790054182948e-05</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="1">
         <v>-0.00010271707597833408</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="1">
         <v>-9.2081775341186153e-06</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="1">
         <v>-7.001061118564951e-05</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="1">
         <v>3.0950299204906423e-06</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="1">
         <v>-0.0005386836053062052</v>
       </c>
-      <c r="O24">
+      <c r="O24" s="1">
         <v>0.00011973015689055282</v>
       </c>
-      <c r="P24">
+      <c r="P24" s="1">
         <v>-1.9510205894155168e-06</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="1">
         <v>-0.00012334006359578792</v>
       </c>
-      <c r="R24">
+      <c r="R24" s="1">
         <v>2.5452738225816007e-05</v>
       </c>
-      <c r="S24">
+      <c r="S24" s="1">
         <v>0.00019293200440824443</v>
       </c>
-      <c r="T24">
+      <c r="T24" s="1">
         <v>-1.3753813432569595e-05</v>
       </c>
-      <c r="U24">
+      <c r="U24" s="1">
         <v>-0.0004001353239428164</v>
       </c>
-      <c r="V24">
+      <c r="V24" s="1">
         <v>-0.00028946290885026316</v>
       </c>
-      <c r="W24">
+      <c r="W24" s="1">
         <v>0.0014819542776581354</v>
       </c>
-      <c r="X24">
+      <c r="X24" s="1">
         <v>0.0012003935401280973</v>
       </c>
-      <c r="Y24">
+      <c r="Y24" s="1">
         <v>0.0025544469924452021</v>
       </c>
-      <c r="Z24">
+      <c r="Z24" s="1">
         <v>0.00012297281633242142</v>
       </c>
-      <c r="AA24">
+      <c r="AA24" s="1">
         <v>-6.5543403202107924e-05</v>
       </c>
-      <c r="AB24">
+      <c r="AB24" s="1">
         <v>-4.1028115713812366e-05</v>
       </c>
-      <c r="AC24">
+      <c r="AC24" s="1">
         <v>9.9799355215764813e-05</v>
       </c>
-      <c r="AD24">
+      <c r="AD24" s="1">
         <v>-9.7089143997352336e-06</v>
       </c>
-      <c r="AE24">
+      <c r="AE24" s="1">
         <v>-0.0016757997747817088</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25">
+        <v>57</v>
+      </c>
+      <c r="B25" s="1">
         <v>0.066296325043422158</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="1">
         <v>-5.9639220337907624e-05</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="1">
         <v>-3.1789624952075824e-05</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="1">
         <v>2.9470200298713153e-07</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="1">
         <v>-8.274622861315431e-06</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="1">
         <v>-3.9261213249722204e-06</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
         <v>1.4577928968700568e-05</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="1">
         <v>-0.00020288103260348959</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="1">
         <v>-7.3754935865742472e-05</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="1">
         <v>-7.6069061098844523e-05</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="1">
         <v>-3.5337271989710787e-06</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="1">
         <v>0.00013008005949504908</v>
       </c>
-      <c r="N25">
+      <c r="N25" s="1">
         <v>0.00036257974665770943</v>
       </c>
-      <c r="O25">
+      <c r="O25" s="1">
         <v>-0.00017477844842983536</v>
       </c>
-      <c r="P25">
+      <c r="P25" s="1">
         <v>-1.1593263959014865e-05</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" s="1">
         <v>-0.00037479259634923268</v>
       </c>
-      <c r="R25">
+      <c r="R25" s="1">
         <v>-0.00022994546565366369</v>
       </c>
-      <c r="S25">
+      <c r="S25" s="1">
         <v>-0.00041692341647540931</v>
       </c>
-      <c r="T25">
+      <c r="T25" s="1">
         <v>-0.00056676069011191849</v>
       </c>
-      <c r="U25">
+      <c r="U25" s="1">
         <v>-0.00052327868167851774</v>
       </c>
-      <c r="V25">
+      <c r="V25" s="1">
         <v>-0.00052767744482099324</v>
       </c>
-      <c r="W25">
+      <c r="W25" s="1">
         <v>-4.7405490455784964e-05</v>
       </c>
-      <c r="X25">
+      <c r="X25" s="1">
         <v>4.4959418244021679e-05</v>
       </c>
-      <c r="Y25">
+      <c r="Y25" s="1">
         <v>0.00012297281633242142</v>
       </c>
-      <c r="Z25">
+      <c r="Z25" s="1">
         <v>0.0023772073930994992</v>
       </c>
-      <c r="AA25">
+      <c r="AA25" s="1">
         <v>0.0017338371740196015</v>
       </c>
-      <c r="AB25">
+      <c r="AB25" s="1">
         <v>0.0017056332193503508</v>
       </c>
-      <c r="AC25">
+      <c r="AC25" s="1">
         <v>0.0017739013654949839</v>
       </c>
-      <c r="AD25">
+      <c r="AD25" s="1">
         <v>-4.0889492647412672e-07</v>
       </c>
-      <c r="AE25">
+      <c r="AE25" s="1">
         <v>-0.00026050471482901152</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26">
+        <v>58</v>
+      </c>
+      <c r="B26" s="1">
         <v>0.041152144884399881</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="1">
         <v>-7.9219937628110788e-05</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="1">
         <v>-7.5855901729021799e-05</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="1">
         <v>6.6148130999926827e-07</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="1">
         <v>3.6117368855440556e-05</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="1">
         <v>0.00018734315537094308</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>-7.8539598587877048e-05</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="1">
         <v>-0.0001955523544125105</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="1">
         <v>0.00026633145562040704</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="1">
         <v>0.00018760173511020981</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="1">
         <v>-2.7597800246015965e-06</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="1">
         <v>-0.0003100072054568739</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="1">
         <v>0.00035269722652658554</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="1">
         <v>-0.00060388969100810472</v>
       </c>
-      <c r="P26">
+      <c r="P26" s="1">
         <v>0.00041861049792983422</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" s="1">
         <v>-0.00061327024037592659</v>
       </c>
-      <c r="R26">
+      <c r="R26" s="1">
         <v>-0.00047457318888571853</v>
       </c>
-      <c r="S26">
+      <c r="S26" s="1">
         <v>-0.00066574719625615841</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="1">
         <v>0.00071006351039425153</v>
       </c>
-      <c r="U26">
+      <c r="U26" s="1">
         <v>0.0012880476859547605</v>
       </c>
-      <c r="V26">
+      <c r="V26" s="1">
         <v>0.0011323823639680011</v>
       </c>
-      <c r="W26">
+      <c r="W26" s="1">
         <v>-0.00049549683331368498</v>
       </c>
-      <c r="X26">
+      <c r="X26" s="1">
         <v>-0.00021971728382072248</v>
       </c>
-      <c r="Y26">
+      <c r="Y26" s="1">
         <v>-6.5543403202107924e-05</v>
       </c>
-      <c r="Z26">
+      <c r="Z26" s="1">
         <v>0.0017338371740196015</v>
       </c>
-      <c r="AA26">
+      <c r="AA26" s="1">
         <v>0.0035420320249977422</v>
       </c>
-      <c r="AB26">
+      <c r="AB26" s="1">
         <v>0.0017482158238569386</v>
       </c>
-      <c r="AC26">
+      <c r="AC26" s="1">
         <v>0.0017669825413808519</v>
       </c>
-      <c r="AD26">
+      <c r="AD26" s="1">
         <v>-8.5754174361370383e-06</v>
       </c>
-      <c r="AE26">
+      <c r="AE26" s="1">
         <v>-1.8005814793751784e-06</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>47</v>
-      </c>
-      <c r="B27">
+        <v>59</v>
+      </c>
+      <c r="B27" s="1">
         <v>0.091026137842238064</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="1">
         <v>3.8405483266120571e-05</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="1">
         <v>-2.1657878400881234e-05</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="1">
         <v>1.2153867929663458e-07</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="1">
         <v>9.2353546964304457e-05</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="1">
         <v>8.1329546932472178e-05</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>7.5939079062429041e-05</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="1">
         <v>6.0704646345669661e-05</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="1">
         <v>7.3325307039152248e-06</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="1">
         <v>-1.7714324571826935e-05</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="1">
         <v>4.0818113271684974e-06</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="1">
         <v>-2.3793157072006491e-06</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="1">
         <v>0.00032703229103266162</v>
       </c>
-      <c r="O27">
+      <c r="O27" s="1">
         <v>-0.00017826341878419538</v>
       </c>
-      <c r="P27">
+      <c r="P27" s="1">
         <v>2.2547775313796657e-05</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" s="1">
         <v>0.00029154219733662154</v>
       </c>
-      <c r="R27">
+      <c r="R27" s="1">
         <v>0.00026546051185756883</v>
       </c>
-      <c r="S27">
+      <c r="S27" s="1">
         <v>8.8498594066968583e-05</v>
       </c>
-      <c r="T27">
+      <c r="T27" s="1">
         <v>0.00015575156277867</v>
       </c>
-      <c r="U27">
+      <c r="U27" s="1">
         <v>6.8721448960805051e-05</v>
       </c>
-      <c r="V27">
+      <c r="V27" s="1">
         <v>2.4245789086180941e-05</v>
       </c>
-      <c r="W27">
+      <c r="W27" s="1">
         <v>-0.00022043506450546613</v>
       </c>
-      <c r="X27">
+      <c r="X27" s="1">
         <v>5.6727730063895095e-05</v>
       </c>
-      <c r="Y27">
+      <c r="Y27" s="1">
         <v>-4.1028115713812366e-05</v>
       </c>
-      <c r="Z27">
+      <c r="Z27" s="1">
         <v>0.0017056332193503508</v>
       </c>
-      <c r="AA27">
+      <c r="AA27" s="1">
         <v>0.0017482158238569386</v>
       </c>
-      <c r="AB27">
+      <c r="AB27" s="1">
         <v>0.002712942747102676</v>
       </c>
-      <c r="AC27">
+      <c r="AC27" s="1">
         <v>0.0017541909605480526</v>
       </c>
-      <c r="AD27">
+      <c r="AD27" s="1">
         <v>1.8766864561028139e-05</v>
       </c>
-      <c r="AE27">
+      <c r="AE27" s="1">
         <v>-0.0015453964933698314</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28">
+        <v>60</v>
+      </c>
+      <c r="B28" s="1">
         <v>0.026413136194878419</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="1">
         <v>-8.478422187331713e-05</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="1">
         <v>-3.3353497673813148e-05</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="1">
         <v>3.3168461507984337e-07</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="1">
         <v>-0.00057841159540590603</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="1">
         <v>-0.0005052037303517453</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>-0.00043920405845935574</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="1">
         <v>-0.00061212124498428826</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="1">
         <v>-5.2816937804775965e-05</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="1">
         <v>2.938214195455412e-05</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="1">
         <v>-4.7167480330407695e-06</v>
       </c>
-      <c r="M28">
+      <c r="M28" s="1">
         <v>8.0303001155676297e-05</v>
       </c>
-      <c r="N28">
+      <c r="N28" s="1">
         <v>0.00030707311059573889</v>
       </c>
-      <c r="O28">
+      <c r="O28" s="1">
         <v>-0.00017719232418892013</v>
       </c>
-      <c r="P28">
+      <c r="P28" s="1">
         <v>-5.6548651036884574e-06</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" s="1">
         <v>-0.00027625801803186911</v>
       </c>
-      <c r="R28">
+      <c r="R28" s="1">
         <v>-0.00025554743819388576</v>
       </c>
-      <c r="S28">
+      <c r="S28" s="1">
         <v>-0.00047840835065110499</v>
       </c>
-      <c r="T28">
+      <c r="T28" s="1">
         <v>1.7833010439959746e-05</v>
       </c>
-      <c r="U28">
+      <c r="U28" s="1">
         <v>0.00017809833788614074</v>
       </c>
-      <c r="V28">
+      <c r="V28" s="1">
         <v>0.00013751175020742384</v>
       </c>
-      <c r="W28">
+      <c r="W28" s="1">
         <v>-0.00014339447218155886</v>
       </c>
-      <c r="X28">
+      <c r="X28" s="1">
         <v>9.8662396590051393e-05</v>
       </c>
-      <c r="Y28">
+      <c r="Y28" s="1">
         <v>9.9799355215764813e-05</v>
       </c>
-      <c r="Z28">
+      <c r="Z28" s="1">
         <v>0.0017739013654949839</v>
       </c>
-      <c r="AA28">
+      <c r="AA28" s="1">
         <v>0.0017669825413808519</v>
       </c>
-      <c r="AB28">
+      <c r="AB28" s="1">
         <v>0.0017541909605480526</v>
       </c>
-      <c r="AC28">
+      <c r="AC28" s="1">
         <v>0.0022784313257508499</v>
       </c>
-      <c r="AD28">
+      <c r="AD28" s="1">
         <v>3.1618460600127044e-07</v>
       </c>
-      <c r="AE28">
+      <c r="AE28" s="1">
         <v>-0.00044282295277743718</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29">
+        <v>61</v>
+      </c>
+      <c r="B29" s="1">
         <v>0.012439449728496744</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="1">
         <v>7.6191141681226573e-06</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="1">
         <v>-1.1085362276545344e-06</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="1">
         <v>8.2156557945128462e-09</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="1">
         <v>9.0671573065469928e-06</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="1">
         <v>-1.2349192065575182e-06</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>-2.129269578395542e-06</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="1">
         <v>1.5926877012795702e-05</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="1">
         <v>-5.7424220582816448e-07</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="1">
         <v>8.4350494529750772e-07</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="1">
         <v>-7.2616839099441904e-07</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="1">
         <v>-8.97690709157089e-06</v>
       </c>
-      <c r="N29">
+      <c r="N29" s="1">
         <v>-1.4065500302039036e-05</v>
       </c>
-      <c r="O29">
+      <c r="O29" s="1">
         <v>-8.2050199883564089e-06</v>
       </c>
-      <c r="P29">
+      <c r="P29" s="1">
         <v>1.2146008325630148e-05</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" s="1">
         <v>6.2893109497402528e-05</v>
       </c>
-      <c r="R29">
+      <c r="R29" s="1">
         <v>3.7520876562416924e-05</v>
       </c>
-      <c r="S29">
+      <c r="S29" s="1">
         <v>2.6651566647904312e-05</v>
       </c>
-      <c r="T29">
+      <c r="T29" s="1">
         <v>1.7057913603004023e-05</v>
       </c>
-      <c r="U29">
+      <c r="U29" s="1">
         <v>1.1252003639994563e-05</v>
       </c>
-      <c r="V29">
+      <c r="V29" s="1">
         <v>-2.9773852312897208e-06</v>
       </c>
-      <c r="W29">
+      <c r="W29" s="1">
         <v>-1.2328893807200166e-05</v>
       </c>
-      <c r="X29">
+      <c r="X29" s="1">
         <v>-1.2377498639513462e-05</v>
       </c>
-      <c r="Y29">
+      <c r="Y29" s="1">
         <v>-9.7089143997352336e-06</v>
       </c>
-      <c r="Z29">
+      <c r="Z29" s="1">
         <v>-4.0889492647412672e-07</v>
       </c>
-      <c r="AA29">
+      <c r="AA29" s="1">
         <v>-8.5754174361370383e-06</v>
       </c>
-      <c r="AB29">
+      <c r="AB29" s="1">
         <v>1.8766864561028139e-05</v>
       </c>
-      <c r="AC29">
+      <c r="AC29" s="1">
         <v>3.1618460600127044e-07</v>
       </c>
-      <c r="AD29">
+      <c r="AD29" s="1">
         <v>1.5505345097440277e-05</v>
       </c>
-      <c r="AE29">
+      <c r="AE29" s="1">
         <v>-0.00022085633634984719</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>50</v>
-      </c>
-      <c r="B30">
+        <v>62</v>
+      </c>
+      <c r="B30" s="1">
         <v>-0.22778654353667704</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="1">
         <v>-0.00066283310454956111</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="1">
         <v>-0.0010483699560981065</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="1">
         <v>1.0640581856787739e-05</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="1">
         <v>-0.032159784235063139</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="1">
         <v>-0.032280126940576095</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>-0.032381623799499062</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="1">
         <v>-0.033017364064007113</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="1">
         <v>0.00054327732350461925</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="1">
         <v>-0.0042891616651933974</v>
       </c>
-      <c r="L30">
+      <c r="L30" s="1">
         <v>0.00020675770649089548</v>
       </c>
-      <c r="M30">
+      <c r="M30" s="1">
         <v>0.00088216900507231283</v>
       </c>
-      <c r="N30">
+      <c r="N30" s="1">
         <v>0.0021511976125625494</v>
       </c>
-      <c r="O30">
+      <c r="O30" s="1">
         <v>-0.0052289910423943256</v>
       </c>
-      <c r="P30">
+      <c r="P30" s="1">
         <v>-0.00057478633349137642</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" s="1">
         <v>-0.026705710144383613</v>
       </c>
-      <c r="R30">
+      <c r="R30" s="1">
         <v>-0.027217721212380534</v>
       </c>
-      <c r="S30">
+      <c r="S30" s="1">
         <v>-0.027175455384372896</v>
       </c>
-      <c r="T30">
+      <c r="T30" s="1">
         <v>-0.038900343883523689</v>
       </c>
-      <c r="U30">
+      <c r="U30" s="1">
         <v>-0.030962458147002658</v>
       </c>
-      <c r="V30">
+      <c r="V30" s="1">
         <v>-0.032909501336933288</v>
       </c>
-      <c r="W30">
+      <c r="W30" s="1">
         <v>-0.00018776335799809745</v>
       </c>
-      <c r="X30">
+      <c r="X30" s="1">
         <v>-0.0033783884902997504</v>
       </c>
-      <c r="Y30">
+      <c r="Y30" s="1">
         <v>-0.0016757997747817088</v>
       </c>
-      <c r="Z30">
+      <c r="Z30" s="1">
         <v>-0.00026050471482901152</v>
       </c>
-      <c r="AA30">
+      <c r="AA30" s="1">
         <v>-1.8005814793751784e-06</v>
       </c>
-      <c r="AB30">
+      <c r="AB30" s="1">
         <v>-0.0015453964933698314</v>
       </c>
-      <c r="AC30">
+      <c r="AC30" s="1">
         <v>-0.00044282295277743718</v>
       </c>
-      <c r="AD30">
+      <c r="AD30" s="1">
         <v>-0.00022085633634984719</v>
       </c>
-      <c r="AE30">
+      <c r="AE30" s="1">
         <v>0.11345934928007138</v>
       </c>
     </row>
